--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="335">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -843,6 +845,183 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
   </si>
 </sst>
 </file>
@@ -22661,4 +22840,1232 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>281</v>
+      </c>
+      <c r="R1" t="s">
+        <v>282</v>
+      </c>
+      <c r="S1" t="s">
+        <v>283</v>
+      </c>
+      <c r="T1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U1" t="s">
+        <v>285</v>
+      </c>
+      <c r="V1" t="s">
+        <v>286</v>
+      </c>
+      <c r="W1" t="s">
+        <v>287</v>
+      </c>
+      <c r="X1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="R2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" t="n">
+        <v>27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="R3" t="n">
+        <v>26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V3" t="n">
+        <v>26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R4" t="n">
+        <v>21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.241</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="R5" t="n">
+        <v>39</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="V5" t="n">
+        <v>39</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="R6" t="n">
+        <v>27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="V6" t="n">
+        <v>27</v>
+      </c>
+      <c r="W6" t="n">
+        <v>21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R7" t="n">
+        <v>24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24</v>
+      </c>
+      <c r="W7" t="n">
+        <v>39</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.876</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R9" t="n">
+        <v>20</v>
+      </c>
+      <c r="S9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V9" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" t="n">
+        <v>21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>26</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22</v>
+      </c>
+      <c r="W10" t="n">
+        <v>26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="R11" t="n">
+        <v>27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="V11" t="n">
+        <v>27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>30</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K1" t="s">
+        <v>302</v>
+      </c>
+      <c r="L1" t="s">
+        <v>303</v>
+      </c>
+      <c r="M1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N1" t="s">
+        <v>305</v>
+      </c>
+      <c r="O1" t="s">
+        <v>306</v>
+      </c>
+      <c r="P1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>320</v>
+      </c>
+      <c r="I2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>322</v>
+      </c>
+      <c r="I4" t="s">
+        <v>327</v>
+      </c>
+      <c r="J4" t="s">
+        <v>332</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>323</v>
+      </c>
+      <c r="I5" t="s">
+        <v>328</v>
+      </c>
+      <c r="J5" t="s">
+        <v>333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>324</v>
+      </c>
+      <c r="I6" t="s">
+        <v>329</v>
+      </c>
+      <c r="J6" t="s">
+        <v>334</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="382">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -966,6 +968,201 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
   </si>
 </sst>
 </file>
@@ -27787,4 +27984,1451 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>322</v>
+      </c>
+      <c r="R1" t="s">
+        <v>323</v>
+      </c>
+      <c r="S1" t="s">
+        <v>324</v>
+      </c>
+      <c r="T1" t="s">
+        <v>325</v>
+      </c>
+      <c r="U1" t="s">
+        <v>326</v>
+      </c>
+      <c r="V1" t="s">
+        <v>327</v>
+      </c>
+      <c r="W1" t="s">
+        <v>328</v>
+      </c>
+      <c r="X1" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="R2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" t="n">
+        <v>27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="R3" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="V3" t="n">
+        <v>56</v>
+      </c>
+      <c r="W3" t="n">
+        <v>28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="R4" t="n">
+        <v>26</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V5" t="n">
+        <v>21</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.241</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="V6" t="n">
+        <v>39</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="R7" t="n">
+        <v>27</v>
+      </c>
+      <c r="S7" t="n">
+        <v>21</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R9" t="n">
+        <v>24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.876</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R10" t="n">
+        <v>20</v>
+      </c>
+      <c r="S10" t="n">
+        <v>21</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V10" t="n">
+        <v>20</v>
+      </c>
+      <c r="W10" t="n">
+        <v>21</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R11" t="n">
+        <v>22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V11" t="n">
+        <v>22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R12" t="n">
+        <v>28</v>
+      </c>
+      <c r="S12" t="n">
+        <v>56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>56</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.697</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="R13" t="n">
+        <v>27</v>
+      </c>
+      <c r="S13" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="V13" t="n">
+        <v>27</v>
+      </c>
+      <c r="W13" t="n">
+        <v>30</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H1" t="s">
+        <v>340</v>
+      </c>
+      <c r="I1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K1" t="s">
+        <v>343</v>
+      </c>
+      <c r="L1" t="s">
+        <v>344</v>
+      </c>
+      <c r="M1" t="s">
+        <v>345</v>
+      </c>
+      <c r="N1" t="s">
+        <v>346</v>
+      </c>
+      <c r="O1" t="s">
+        <v>347</v>
+      </c>
+      <c r="P1" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I4" t="s">
+        <v>372</v>
+      </c>
+      <c r="J4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>367</v>
+      </c>
+      <c r="I5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J5" t="s">
+        <v>379</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>362</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>368</v>
+      </c>
+      <c r="I6" t="s">
+        <v>374</v>
+      </c>
+      <c r="J6" t="s">
+        <v>380</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7" t="s">
+        <v>375</v>
+      </c>
+      <c r="J7" t="s">
+        <v>381</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="464">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1179,6 +1181,234 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
   </si>
 </sst>
 </file>
@@ -35526,4 +35756,1889 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>393</v>
+      </c>
+      <c r="R1" t="s">
+        <v>394</v>
+      </c>
+      <c r="S1" t="s">
+        <v>395</v>
+      </c>
+      <c r="T1" t="s">
+        <v>396</v>
+      </c>
+      <c r="U1" t="s">
+        <v>397</v>
+      </c>
+      <c r="V1" t="s">
+        <v>398</v>
+      </c>
+      <c r="W1" t="s">
+        <v>399</v>
+      </c>
+      <c r="X1" t="s">
+        <v>400</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>401</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="R2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" t="n">
+        <v>27</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="R3" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="V3" t="n">
+        <v>56</v>
+      </c>
+      <c r="W3" t="n">
+        <v>28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="R4" t="n">
+        <v>26</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="V5" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R6" t="n">
+        <v>19</v>
+      </c>
+      <c r="S6" t="n">
+        <v>27</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V6" t="n">
+        <v>19</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.329</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R7" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>20</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.241</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>39</v>
+      </c>
+      <c r="S8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="V8" t="n">
+        <v>39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="R9" t="n">
+        <v>27</v>
+      </c>
+      <c r="S9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>21</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R10" t="n">
+        <v>21</v>
+      </c>
+      <c r="S10" t="n">
+        <v>27</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V10" t="n">
+        <v>21</v>
+      </c>
+      <c r="W10" t="n">
+        <v>27</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R11" t="n">
+        <v>24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>39</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24</v>
+      </c>
+      <c r="W11" t="n">
+        <v>39</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.876</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="R12" t="n">
+        <v>27</v>
+      </c>
+      <c r="S12" t="n">
+        <v>19</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="V12" t="n">
+        <v>27</v>
+      </c>
+      <c r="W12" t="n">
+        <v>19</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20</v>
+      </c>
+      <c r="S13" t="n">
+        <v>32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W13" t="n">
+        <v>32</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R14" t="n">
+        <v>20</v>
+      </c>
+      <c r="S14" t="n">
+        <v>21</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V14" t="n">
+        <v>20</v>
+      </c>
+      <c r="W14" t="n">
+        <v>21</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R15" t="n">
+        <v>22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V15" t="n">
+        <v>22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R16" t="n">
+        <v>28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>56</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V16" t="n">
+        <v>28</v>
+      </c>
+      <c r="W16" t="n">
+        <v>56</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.697</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="R17" t="n">
+        <v>27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="V17" t="n">
+        <v>27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>30</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J1" t="s">
+        <v>413</v>
+      </c>
+      <c r="K1" t="s">
+        <v>414</v>
+      </c>
+      <c r="L1" t="s">
+        <v>415</v>
+      </c>
+      <c r="M1" t="s">
+        <v>416</v>
+      </c>
+      <c r="N1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O1" t="s">
+        <v>418</v>
+      </c>
+      <c r="P1" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J2" t="s">
+        <v>456</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>441</v>
+      </c>
+      <c r="I3" t="s">
+        <v>449</v>
+      </c>
+      <c r="J3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>434</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>442</v>
+      </c>
+      <c r="I4" t="s">
+        <v>450</v>
+      </c>
+      <c r="J4" t="s">
+        <v>458</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I5" t="s">
+        <v>451</v>
+      </c>
+      <c r="J5" t="s">
+        <v>459</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>444</v>
+      </c>
+      <c r="I6" t="s">
+        <v>452</v>
+      </c>
+      <c r="J6" t="s">
+        <v>460</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>437</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>445</v>
+      </c>
+      <c r="I7" t="s">
+        <v>453</v>
+      </c>
+      <c r="J7" t="s">
+        <v>461</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>423</v>
+      </c>
+      <c r="B8" t="s">
+        <v>430</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>438</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>446</v>
+      </c>
+      <c r="I8" t="s">
+        <v>454</v>
+      </c>
+      <c r="J8" t="s">
+        <v>462</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>439</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>447</v>
+      </c>
+      <c r="I9" t="s">
+        <v>455</v>
+      </c>
+      <c r="J9" t="s">
+        <v>463</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="551">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1407,6 +1409,267 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
   </si>
 </sst>
 </file>
@@ -42420,4 +42683,2321 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>469</v>
+      </c>
+      <c r="R1" t="s">
+        <v>470</v>
+      </c>
+      <c r="S1" t="s">
+        <v>471</v>
+      </c>
+      <c r="T1" t="s">
+        <v>472</v>
+      </c>
+      <c r="U1" t="s">
+        <v>473</v>
+      </c>
+      <c r="V1" t="s">
+        <v>474</v>
+      </c>
+      <c r="W1" t="s">
+        <v>475</v>
+      </c>
+      <c r="X1" t="s">
+        <v>476</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>478</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="R2" t="n">
+        <v>28</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="V2" t="n">
+        <v>28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.817</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="R3" t="n">
+        <v>30</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="V3" t="n">
+        <v>30</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="R4" t="n">
+        <v>56</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="V4" t="n">
+        <v>56</v>
+      </c>
+      <c r="W4" t="n">
+        <v>28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="R5" t="n">
+        <v>26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.278</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R6" t="n">
+        <v>32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="V6" t="n">
+        <v>32</v>
+      </c>
+      <c r="W6" t="n">
+        <v>20</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R7" t="n">
+        <v>19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>27</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.329</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R8" t="n">
+        <v>21</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>20</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.241</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="R9" t="n">
+        <v>18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="V9" t="n">
+        <v>18</v>
+      </c>
+      <c r="W9" t="n">
+        <v>26</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.706</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="V10" t="n">
+        <v>39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="R11" t="n">
+        <v>27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>21</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="V11" t="n">
+        <v>27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>21</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R12" t="n">
+        <v>21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V12" t="n">
+        <v>21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>27</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R13" t="n">
+        <v>24</v>
+      </c>
+      <c r="S13" t="n">
+        <v>39</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="V13" t="n">
+        <v>24</v>
+      </c>
+      <c r="W13" t="n">
+        <v>39</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.876</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="R14" t="n">
+        <v>27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="V14" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" t="n">
+        <v>19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="R15" t="n">
+        <v>26</v>
+      </c>
+      <c r="S15" t="n">
+        <v>18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="V15" t="n">
+        <v>26</v>
+      </c>
+      <c r="W15" t="n">
+        <v>18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R16" t="n">
+        <v>20</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V16" t="n">
+        <v>20</v>
+      </c>
+      <c r="W16" t="n">
+        <v>21</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="R17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="V17" t="n">
+        <v>20</v>
+      </c>
+      <c r="W17" t="n">
+        <v>32</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R18" t="n">
+        <v>22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>26</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22</v>
+      </c>
+      <c r="W18" t="n">
+        <v>26</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R19" t="n">
+        <v>28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>56</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V19" t="n">
+        <v>28</v>
+      </c>
+      <c r="W19" t="n">
+        <v>56</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.697</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="R20" t="n">
+        <v>27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="V20" t="n">
+        <v>27</v>
+      </c>
+      <c r="W20" t="n">
+        <v>30</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>28</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="V21" t="n">
+        <v>10</v>
+      </c>
+      <c r="W21" t="n">
+        <v>28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.817</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1" t="s">
+        <v>488</v>
+      </c>
+      <c r="J1" t="s">
+        <v>489</v>
+      </c>
+      <c r="K1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L1" t="s">
+        <v>491</v>
+      </c>
+      <c r="M1" t="s">
+        <v>492</v>
+      </c>
+      <c r="N1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O1" t="s">
+        <v>494</v>
+      </c>
+      <c r="P1" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>521</v>
+      </c>
+      <c r="I2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J2" t="s">
+        <v>541</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>523</v>
+      </c>
+      <c r="I4" t="s">
+        <v>533</v>
+      </c>
+      <c r="J4" t="s">
+        <v>543</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>514</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>524</v>
+      </c>
+      <c r="I5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J5" t="s">
+        <v>544</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>525</v>
+      </c>
+      <c r="I6" t="s">
+        <v>535</v>
+      </c>
+      <c r="J6" t="s">
+        <v>545</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I7" t="s">
+        <v>536</v>
+      </c>
+      <c r="J7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>527</v>
+      </c>
+      <c r="I8" t="s">
+        <v>537</v>
+      </c>
+      <c r="J8" t="s">
+        <v>547</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>518</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>528</v>
+      </c>
+      <c r="I9" t="s">
+        <v>538</v>
+      </c>
+      <c r="J9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>500</v>
+      </c>
+      <c r="B10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>529</v>
+      </c>
+      <c r="I10" t="s">
+        <v>539</v>
+      </c>
+      <c r="J10" t="s">
+        <v>549</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" t="s">
+        <v>510</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>520</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>530</v>
+      </c>
+      <c r="I11" t="s">
+        <v>540</v>
+      </c>
+      <c r="J11" t="s">
+        <v>550</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="551">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44439,7 +44439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,6 +2362,569 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I1" t="s">
+        <v>488</v>
+      </c>
+      <c r="J1" t="s">
+        <v>489</v>
+      </c>
+      <c r="K1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L1" t="s">
+        <v>491</v>
+      </c>
+      <c r="M1" t="s">
+        <v>492</v>
+      </c>
+      <c r="N1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O1" t="s">
+        <v>494</v>
+      </c>
+      <c r="P1" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>521</v>
+      </c>
+      <c r="I2" t="s">
+        <v>531</v>
+      </c>
+      <c r="J2" t="s">
+        <v>541</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>512</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>522</v>
+      </c>
+      <c r="I3" t="s">
+        <v>532</v>
+      </c>
+      <c r="J3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>523</v>
+      </c>
+      <c r="I4" t="s">
+        <v>533</v>
+      </c>
+      <c r="J4" t="s">
+        <v>543</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>514</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>524</v>
+      </c>
+      <c r="I5" t="s">
+        <v>534</v>
+      </c>
+      <c r="J5" t="s">
+        <v>544</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>515</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>525</v>
+      </c>
+      <c r="I6" t="s">
+        <v>535</v>
+      </c>
+      <c r="J6" t="s">
+        <v>545</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I7" t="s">
+        <v>536</v>
+      </c>
+      <c r="J7" t="s">
+        <v>546</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>517</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>527</v>
+      </c>
+      <c r="I8" t="s">
+        <v>537</v>
+      </c>
+      <c r="J8" t="s">
+        <v>547</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>518</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>528</v>
+      </c>
+      <c r="I9" t="s">
+        <v>538</v>
+      </c>
+      <c r="J9" t="s">
+        <v>548</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>500</v>
+      </c>
+      <c r="B10" t="s">
+        <v>509</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>529</v>
+      </c>
+      <c r="I10" t="s">
+        <v>539</v>
+      </c>
+      <c r="J10" t="s">
+        <v>549</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" t="s">
+        <v>510</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>520</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>530</v>
+      </c>
+      <c r="I11" t="s">
+        <v>540</v>
+      </c>
+      <c r="J11" t="s">
+        <v>550</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -44437,567 +45000,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D1" t="s">
-        <v>483</v>
-      </c>
-      <c r="E1" t="s">
-        <v>484</v>
-      </c>
-      <c r="F1" t="s">
-        <v>485</v>
-      </c>
-      <c r="G1" t="s">
-        <v>486</v>
-      </c>
-      <c r="H1" t="s">
-        <v>487</v>
-      </c>
-      <c r="I1" t="s">
-        <v>488</v>
-      </c>
-      <c r="J1" t="s">
-        <v>489</v>
-      </c>
-      <c r="K1" t="s">
-        <v>490</v>
-      </c>
-      <c r="L1" t="s">
-        <v>491</v>
-      </c>
-      <c r="M1" t="s">
-        <v>492</v>
-      </c>
-      <c r="N1" t="s">
-        <v>493</v>
-      </c>
-      <c r="O1" t="s">
-        <v>494</v>
-      </c>
-      <c r="P1" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J2" t="s">
-        <v>541</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>512</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>522</v>
-      </c>
-      <c r="I3" t="s">
-        <v>532</v>
-      </c>
-      <c r="J3" t="s">
-        <v>542</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>497</v>
-      </c>
-      <c r="B4" t="s">
-        <v>503</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>513</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>523</v>
-      </c>
-      <c r="I4" t="s">
-        <v>533</v>
-      </c>
-      <c r="J4" t="s">
-        <v>543</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>497</v>
-      </c>
-      <c r="B5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>514</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>524</v>
-      </c>
-      <c r="I5" t="s">
-        <v>534</v>
-      </c>
-      <c r="J5" t="s">
-        <v>544</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" t="s">
-        <v>505</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>515</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>525</v>
-      </c>
-      <c r="I6" t="s">
-        <v>535</v>
-      </c>
-      <c r="J6" t="s">
-        <v>545</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>498</v>
-      </c>
-      <c r="B7" t="s">
-        <v>506</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>516</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>526</v>
-      </c>
-      <c r="I7" t="s">
-        <v>536</v>
-      </c>
-      <c r="J7" t="s">
-        <v>546</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>499</v>
-      </c>
-      <c r="B8" t="s">
-        <v>507</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>517</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>527</v>
-      </c>
-      <c r="I8" t="s">
-        <v>537</v>
-      </c>
-      <c r="J8" t="s">
-        <v>547</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>499</v>
-      </c>
-      <c r="B9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>518</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>528</v>
-      </c>
-      <c r="I9" t="s">
-        <v>538</v>
-      </c>
-      <c r="J9" t="s">
-        <v>548</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>500</v>
-      </c>
-      <c r="B10" t="s">
-        <v>509</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>519</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>529</v>
-      </c>
-      <c r="I10" t="s">
-        <v>539</v>
-      </c>
-      <c r="J10" t="s">
-        <v>549</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>500</v>
-      </c>
-      <c r="B11" t="s">
-        <v>510</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>520</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>530</v>
-      </c>
-      <c r="I11" t="s">
-        <v>540</v>
-      </c>
-      <c r="J11" t="s">
-        <v>550</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
+    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
+    <sheet name="Stand2" sheetId="16" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="17"/>
   </sheets>
 </workbook>
 </file>
@@ -2362,7 +2362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="622">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1563,6 +1565,324 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
   </si>
 </sst>
 </file>
@@ -57571,4 +57891,2621 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>521</v>
+      </c>
+      <c r="R1" t="s">
+        <v>522</v>
+      </c>
+      <c r="S1" t="s">
+        <v>523</v>
+      </c>
+      <c r="T1" t="s">
+        <v>524</v>
+      </c>
+      <c r="U1" t="s">
+        <v>525</v>
+      </c>
+      <c r="V1" t="s">
+        <v>526</v>
+      </c>
+      <c r="W1" t="s">
+        <v>527</v>
+      </c>
+      <c r="X1" t="s">
+        <v>528</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>529</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R2" t="n">
+        <v>70</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>86</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V3" t="n">
+        <v>43</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R4" t="n">
+        <v>62</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R6" t="n">
+        <v>75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="V6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.938</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>55</v>
+      </c>
+      <c r="S7" t="n">
+        <v>36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.5815</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.6565</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0749999999999997</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.238</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="R8" t="n">
+        <v>41</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.2265</v>
+      </c>
+      <c r="V8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.172</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="R9" t="n">
+        <v>76</v>
+      </c>
+      <c r="S9" t="n">
+        <v>86</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="V9" t="n">
+        <v>38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>43</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="R10" t="n">
+        <v>40</v>
+      </c>
+      <c r="S10" t="n">
+        <v>52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="V10" t="n">
+        <v>20</v>
+      </c>
+      <c r="W10" t="n">
+        <v>26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.0489999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R11" t="n">
+        <v>32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="V11" t="n">
+        <v>32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>96</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="V12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>48</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.0695</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.7005</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R13" t="n">
+        <v>21</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V13" t="n">
+        <v>21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>27</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="R14" t="n">
+        <v>24</v>
+      </c>
+      <c r="S14" t="n">
+        <v>39</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="V14" t="n">
+        <v>24</v>
+      </c>
+      <c r="W14" t="n">
+        <v>39</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.876</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.626</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="R15" t="n">
+        <v>27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>19</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="V15" t="n">
+        <v>27</v>
+      </c>
+      <c r="W15" t="n">
+        <v>19</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="R16" t="n">
+        <v>26</v>
+      </c>
+      <c r="S16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="V16" t="n">
+        <v>26</v>
+      </c>
+      <c r="W16" t="n">
+        <v>18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="R17" t="n">
+        <v>28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>73</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.2915</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5025</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>20</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V18" t="n">
+        <v>20</v>
+      </c>
+      <c r="W18" t="n">
+        <v>21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R19" t="n">
+        <v>22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22</v>
+      </c>
+      <c r="W19" t="n">
+        <v>26</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="R20" t="n">
+        <v>41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V20" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>33</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="R21" t="n">
+        <v>10</v>
+      </c>
+      <c r="S21" t="n">
+        <v>28</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="V21" t="n">
+        <v>10</v>
+      </c>
+      <c r="W21" t="n">
+        <v>28</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.817</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B1" t="s">
+        <v>533</v>
+      </c>
+      <c r="C1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G1" t="s">
+        <v>538</v>
+      </c>
+      <c r="H1" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1" t="s">
+        <v>540</v>
+      </c>
+      <c r="J1" t="s">
+        <v>541</v>
+      </c>
+      <c r="K1" t="s">
+        <v>542</v>
+      </c>
+      <c r="L1" t="s">
+        <v>543</v>
+      </c>
+      <c r="M1" t="s">
+        <v>544</v>
+      </c>
+      <c r="N1" t="s">
+        <v>545</v>
+      </c>
+      <c r="O1" t="s">
+        <v>546</v>
+      </c>
+      <c r="P1" t="s">
+        <v>547</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J2" t="s">
+        <v>606</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>575</v>
+      </c>
+      <c r="I3" t="s">
+        <v>591</v>
+      </c>
+      <c r="J3" t="s">
+        <v>607</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>568</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>576</v>
+      </c>
+      <c r="I4" t="s">
+        <v>592</v>
+      </c>
+      <c r="J4" t="s">
+        <v>608</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>567</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>577</v>
+      </c>
+      <c r="I5" t="s">
+        <v>593</v>
+      </c>
+      <c r="J5" t="s">
+        <v>609</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>566</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>578</v>
+      </c>
+      <c r="I6" t="s">
+        <v>594</v>
+      </c>
+      <c r="J6" t="s">
+        <v>610</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>550</v>
+      </c>
+      <c r="B7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>564</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>579</v>
+      </c>
+      <c r="I7" t="s">
+        <v>595</v>
+      </c>
+      <c r="J7" t="s">
+        <v>611</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>560</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>571</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>580</v>
+      </c>
+      <c r="I8" t="s">
+        <v>596</v>
+      </c>
+      <c r="J8" t="s">
+        <v>612</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>551</v>
+      </c>
+      <c r="B9" t="s">
+        <v>561</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>572</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>581</v>
+      </c>
+      <c r="I9" t="s">
+        <v>597</v>
+      </c>
+      <c r="J9" t="s">
+        <v>613</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>552</v>
+      </c>
+      <c r="B10" t="s">
+        <v>562</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>582</v>
+      </c>
+      <c r="I10" t="s">
+        <v>598</v>
+      </c>
+      <c r="J10" t="s">
+        <v>614</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>552</v>
+      </c>
+      <c r="B11" t="s">
+        <v>563</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>573</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>583</v>
+      </c>
+      <c r="I11" t="s">
+        <v>599</v>
+      </c>
+      <c r="J11" t="s">
+        <v>615</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>553</v>
+      </c>
+      <c r="B12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>563</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>584</v>
+      </c>
+      <c r="I12" t="s">
+        <v>600</v>
+      </c>
+      <c r="J12" t="s">
+        <v>616</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B13" t="s">
+        <v>565</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>561</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>585</v>
+      </c>
+      <c r="I13" t="s">
+        <v>601</v>
+      </c>
+      <c r="J13" t="s">
+        <v>617</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>553</v>
+      </c>
+      <c r="B14" t="s">
+        <v>566</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>559</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>586</v>
+      </c>
+      <c r="I14" t="s">
+        <v>602</v>
+      </c>
+      <c r="J14" t="s">
+        <v>618</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>553</v>
+      </c>
+      <c r="B15" t="s">
+        <v>567</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>558</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>587</v>
+      </c>
+      <c r="I15" t="s">
+        <v>603</v>
+      </c>
+      <c r="J15" t="s">
+        <v>619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>553</v>
+      </c>
+      <c r="B16" t="s">
+        <v>568</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>554</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>588</v>
+      </c>
+      <c r="I16" t="s">
+        <v>604</v>
+      </c>
+      <c r="J16" t="s">
+        <v>620</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>553</v>
+      </c>
+      <c r="B17" t="s">
+        <v>569</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>560</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>589</v>
+      </c>
+      <c r="I17" t="s">
+        <v>605</v>
+      </c>
+      <c r="J17" t="s">
+        <v>621</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="635">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1590,6 +1592,336 @@
   </si>
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
   </si>
 </sst>
 </file>
@@ -59567,4 +59899,2668 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P1" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>530</v>
+      </c>
+      <c r="R1" t="s">
+        <v>531</v>
+      </c>
+      <c r="S1" t="s">
+        <v>532</v>
+      </c>
+      <c r="T1" t="s">
+        <v>533</v>
+      </c>
+      <c r="U1" t="s">
+        <v>534</v>
+      </c>
+      <c r="V1" t="s">
+        <v>535</v>
+      </c>
+      <c r="W1" t="s">
+        <v>536</v>
+      </c>
+      <c r="X1" t="s">
+        <v>537</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>538</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R2" t="n">
+        <v>70</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>86</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V3" t="n">
+        <v>43</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R4" t="n">
+        <v>62</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R6" t="n">
+        <v>75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="V6" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.938</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>55</v>
+      </c>
+      <c r="S7" t="n">
+        <v>36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.5815</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.6565</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0749999999999997</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.238</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="R8" t="n">
+        <v>41</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.2265</v>
+      </c>
+      <c r="V8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.172</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="R9" t="n">
+        <v>76</v>
+      </c>
+      <c r="S9" t="n">
+        <v>86</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="V9" t="n">
+        <v>38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>43</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.423</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="R10" t="n">
+        <v>37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>49</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.2115</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="V10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.0575000000000001</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.3655</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="R11" t="n">
+        <v>40</v>
+      </c>
+      <c r="S11" t="n">
+        <v>52</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="V11" t="n">
+        <v>20</v>
+      </c>
+      <c r="W11" t="n">
+        <v>26</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0489999999999999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="R12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" t="n">
+        <v>66</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="V12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>33</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R13" t="n">
+        <v>32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="V13" t="n">
+        <v>32</v>
+      </c>
+      <c r="W13" t="n">
+        <v>20</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R14" t="n">
+        <v>45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>96</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="V14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>48</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.0695</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.7005</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="R15" t="n">
+        <v>21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>27</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="V15" t="n">
+        <v>21</v>
+      </c>
+      <c r="W15" t="n">
+        <v>27</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="R16" t="n">
+        <v>27</v>
+      </c>
+      <c r="S16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="V16" t="n">
+        <v>27</v>
+      </c>
+      <c r="W16" t="n">
+        <v>19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.811</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="R17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="V17" t="n">
+        <v>26</v>
+      </c>
+      <c r="W17" t="n">
+        <v>18</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.384</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="R18" t="n">
+        <v>20</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V18" t="n">
+        <v>20</v>
+      </c>
+      <c r="W18" t="n">
+        <v>21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="R19" t="n">
+        <v>22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>26</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22</v>
+      </c>
+      <c r="W19" t="n">
+        <v>26</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="R20" t="n">
+        <v>28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>73</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="V20" t="n">
+        <v>14</v>
+      </c>
+      <c r="W20" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.2915</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="R21" t="n">
+        <v>41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>66</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>33</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G1" t="s">
+        <v>547</v>
+      </c>
+      <c r="H1" t="s">
+        <v>548</v>
+      </c>
+      <c r="I1" t="s">
+        <v>549</v>
+      </c>
+      <c r="J1" t="s">
+        <v>550</v>
+      </c>
+      <c r="K1" t="s">
+        <v>551</v>
+      </c>
+      <c r="L1" t="s">
+        <v>552</v>
+      </c>
+      <c r="M1" t="s">
+        <v>553</v>
+      </c>
+      <c r="N1" t="s">
+        <v>554</v>
+      </c>
+      <c r="O1" t="s">
+        <v>555</v>
+      </c>
+      <c r="P1" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>584</v>
+      </c>
+      <c r="I2" t="s">
+        <v>601</v>
+      </c>
+      <c r="J2" t="s">
+        <v>618</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>579</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>585</v>
+      </c>
+      <c r="I3" t="s">
+        <v>602</v>
+      </c>
+      <c r="J3" t="s">
+        <v>619</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I4" t="s">
+        <v>603</v>
+      </c>
+      <c r="J4" t="s">
+        <v>620</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>577</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>587</v>
+      </c>
+      <c r="I5" t="s">
+        <v>604</v>
+      </c>
+      <c r="J5" t="s">
+        <v>621</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>576</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>588</v>
+      </c>
+      <c r="I6" t="s">
+        <v>605</v>
+      </c>
+      <c r="J6" t="s">
+        <v>622</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>574</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>589</v>
+      </c>
+      <c r="I7" t="s">
+        <v>606</v>
+      </c>
+      <c r="J7" t="s">
+        <v>623</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B8" t="s">
+        <v>570</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>582</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>590</v>
+      </c>
+      <c r="I8" t="s">
+        <v>607</v>
+      </c>
+      <c r="J8" t="s">
+        <v>624</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>560</v>
+      </c>
+      <c r="B9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>583</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>591</v>
+      </c>
+      <c r="I9" t="s">
+        <v>608</v>
+      </c>
+      <c r="J9" t="s">
+        <v>625</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B10" t="s">
+        <v>572</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>575</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>592</v>
+      </c>
+      <c r="I10" t="s">
+        <v>609</v>
+      </c>
+      <c r="J10" t="s">
+        <v>626</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>561</v>
+      </c>
+      <c r="B11" t="s">
+        <v>573</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>580</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>593</v>
+      </c>
+      <c r="I11" t="s">
+        <v>610</v>
+      </c>
+      <c r="J11" t="s">
+        <v>627</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>562</v>
+      </c>
+      <c r="B12" t="s">
+        <v>574</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>573</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>594</v>
+      </c>
+      <c r="I12" t="s">
+        <v>611</v>
+      </c>
+      <c r="J12" t="s">
+        <v>628</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>562</v>
+      </c>
+      <c r="B13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>571</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>595</v>
+      </c>
+      <c r="I13" t="s">
+        <v>612</v>
+      </c>
+      <c r="J13" t="s">
+        <v>629</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>562</v>
+      </c>
+      <c r="B14" t="s">
+        <v>576</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>569</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>596</v>
+      </c>
+      <c r="I14" t="s">
+        <v>613</v>
+      </c>
+      <c r="J14" t="s">
+        <v>630</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>562</v>
+      </c>
+      <c r="B15" t="s">
+        <v>577</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>568</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>597</v>
+      </c>
+      <c r="I15" t="s">
+        <v>614</v>
+      </c>
+      <c r="J15" t="s">
+        <v>631</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>562</v>
+      </c>
+      <c r="B16" t="s">
+        <v>578</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>564</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>598</v>
+      </c>
+      <c r="I16" t="s">
+        <v>615</v>
+      </c>
+      <c r="J16" t="s">
+        <v>632</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" t="s">
+        <v>579</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>570</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>599</v>
+      </c>
+      <c r="I17" t="s">
+        <v>616</v>
+      </c>
+      <c r="J17" t="s">
+        <v>633</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>563</v>
+      </c>
+      <c r="B18" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>567</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>600</v>
+      </c>
+      <c r="I18" t="s">
+        <v>617</v>
+      </c>
+      <c r="J18" t="s">
+        <v>634</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="635">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -61655,7 +61655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="676">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1684,6 +1686,366 @@
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
   </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>7.99%</t>
+  </si>
+  <si>
+    <t>23.96%</t>
+  </si>
+  <si>
+    <t>1.46%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>11.92%</t>
+  </si>
+  <si>
+    <t>18.46%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>80.09%</t>
+  </si>
+  <si>
+    <t>57.58%</t>
+  </si>
+  <si>
+    <t>93.44%</t>
+  </si>
 </sst>
 </file>
 
@@ -68960,4 +69322,2815 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>561</v>
+      </c>
+      <c r="R1" t="s">
+        <v>562</v>
+      </c>
+      <c r="S1" t="s">
+        <v>563</v>
+      </c>
+      <c r="T1" t="s">
+        <v>564</v>
+      </c>
+      <c r="U1" t="s">
+        <v>565</v>
+      </c>
+      <c r="V1" t="s">
+        <v>566</v>
+      </c>
+      <c r="W1" t="s">
+        <v>567</v>
+      </c>
+      <c r="X1" t="s">
+        <v>568</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>569</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R2" t="n">
+        <v>70</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R3" t="n">
+        <v>86</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V3" t="n">
+        <v>43</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R4" t="n">
+        <v>62</v>
+      </c>
+      <c r="S4" t="n">
+        <v>28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V4" t="n">
+        <v>31</v>
+      </c>
+      <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>45</v>
+      </c>
+      <c r="S5" t="n">
+        <v>49</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.603</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="R6" t="n">
+        <v>49</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.8015</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.0935</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.895</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R7" t="n">
+        <v>75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>38</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="V7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>19</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.938</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="R8" t="n">
+        <v>54</v>
+      </c>
+      <c r="S8" t="n">
+        <v>38</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4425</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="V8" t="n">
+        <v>27</v>
+      </c>
+      <c r="W8" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.7295</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.1555</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.542</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>46</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V9" t="n">
+        <v>26</v>
+      </c>
+      <c r="W9" t="n">
+        <v>23</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0409999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.313</v>
+      </c>
+      <c r="R10" t="n">
+        <v>55</v>
+      </c>
+      <c r="S10" t="n">
+        <v>36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.5815</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6565</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.0749999999999997</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.238</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.453</v>
+      </c>
+      <c r="R11" t="n">
+        <v>41</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.4645</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.2265</v>
+      </c>
+      <c r="V11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="R12" t="n">
+        <v>60</v>
+      </c>
+      <c r="S12" t="n">
+        <v>46</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.6315</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="V12" t="n">
+        <v>30</v>
+      </c>
+      <c r="W12" t="n">
+        <v>23</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.8085</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.172</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="R13" t="n">
+        <v>76</v>
+      </c>
+      <c r="S13" t="n">
+        <v>86</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="V13" t="n">
+        <v>38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>43</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.828</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.423</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="R14" t="n">
+        <v>37</v>
+      </c>
+      <c r="S14" t="n">
+        <v>49</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.2115</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="V14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0575000000000001</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3655</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.536</v>
+      </c>
+      <c r="R15" t="n">
+        <v>40</v>
+      </c>
+      <c r="S15" t="n">
+        <v>52</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="V15" t="n">
+        <v>20</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0489999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="R16" t="n">
+        <v>45</v>
+      </c>
+      <c r="S16" t="n">
+        <v>66</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="V16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>33</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>38</v>
+      </c>
+      <c r="S17" t="n">
+        <v>61</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="V17" t="n">
+        <v>19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.911</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="R18" t="n">
+        <v>45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>96</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.3155</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.385</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.0695</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.7005</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="R19" t="n">
+        <v>39</v>
+      </c>
+      <c r="S19" t="n">
+        <v>46</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="V19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>23</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.4045</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.5445</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.211</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.794</v>
+      </c>
+      <c r="R20" t="n">
+        <v>28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>73</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.397</v>
+      </c>
+      <c r="V20" t="n">
+        <v>14</v>
+      </c>
+      <c r="W20" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.2915</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="R21" t="n">
+        <v>41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>66</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>33</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" t="s">
+        <v>581</v>
+      </c>
+      <c r="K1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L1" t="s">
+        <v>583</v>
+      </c>
+      <c r="M1" t="s">
+        <v>584</v>
+      </c>
+      <c r="N1" t="s">
+        <v>585</v>
+      </c>
+      <c r="O1" t="s">
+        <v>586</v>
+      </c>
+      <c r="P1" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>616</v>
+      </c>
+      <c r="I2" t="s">
+        <v>636</v>
+      </c>
+      <c r="J2" t="s">
+        <v>656</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>617</v>
+      </c>
+      <c r="I3" t="s">
+        <v>637</v>
+      </c>
+      <c r="J3" t="s">
+        <v>657</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>618</v>
+      </c>
+      <c r="I4" t="s">
+        <v>638</v>
+      </c>
+      <c r="J4" t="s">
+        <v>658</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>609</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>619</v>
+      </c>
+      <c r="I5" t="s">
+        <v>639</v>
+      </c>
+      <c r="J5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>608</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>620</v>
+      </c>
+      <c r="I6" t="s">
+        <v>640</v>
+      </c>
+      <c r="J6" t="s">
+        <v>660</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>606</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>621</v>
+      </c>
+      <c r="I7" t="s">
+        <v>641</v>
+      </c>
+      <c r="J7" t="s">
+        <v>661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>602</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>622</v>
+      </c>
+      <c r="I8" t="s">
+        <v>642</v>
+      </c>
+      <c r="J8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>623</v>
+      </c>
+      <c r="I9" t="s">
+        <v>643</v>
+      </c>
+      <c r="J9" t="s">
+        <v>663</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>592</v>
+      </c>
+      <c r="B10" t="s">
+        <v>604</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I10" t="s">
+        <v>644</v>
+      </c>
+      <c r="J10" t="s">
+        <v>664</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B11" t="s">
+        <v>605</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>612</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>625</v>
+      </c>
+      <c r="I11" t="s">
+        <v>645</v>
+      </c>
+      <c r="J11" t="s">
+        <v>665</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I12" t="s">
+        <v>646</v>
+      </c>
+      <c r="J12" t="s">
+        <v>666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>593</v>
+      </c>
+      <c r="B13" t="s">
+        <v>607</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>603</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>627</v>
+      </c>
+      <c r="I13" t="s">
+        <v>647</v>
+      </c>
+      <c r="J13" t="s">
+        <v>667</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
+        <v>608</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>601</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>628</v>
+      </c>
+      <c r="I14" t="s">
+        <v>648</v>
+      </c>
+      <c r="J14" t="s">
+        <v>668</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" t="s">
+        <v>609</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>629</v>
+      </c>
+      <c r="I15" t="s">
+        <v>649</v>
+      </c>
+      <c r="J15" t="s">
+        <v>669</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>596</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>630</v>
+      </c>
+      <c r="I16" t="s">
+        <v>650</v>
+      </c>
+      <c r="J16" t="s">
+        <v>670</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>593</v>
+      </c>
+      <c r="B17" t="s">
+        <v>611</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>602</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>631</v>
+      </c>
+      <c r="I17" t="s">
+        <v>651</v>
+      </c>
+      <c r="J17" t="s">
+        <v>671</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B18" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>599</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>632</v>
+      </c>
+      <c r="I18" t="s">
+        <v>652</v>
+      </c>
+      <c r="J18" t="s">
+        <v>672</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>597</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>633</v>
+      </c>
+      <c r="I19" t="s">
+        <v>653</v>
+      </c>
+      <c r="J19" t="s">
+        <v>673</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>634</v>
+      </c>
+      <c r="I20" t="s">
+        <v>654</v>
+      </c>
+      <c r="J20" t="s">
+        <v>674</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B21" t="s">
+        <v>615</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>635</v>
+      </c>
+      <c r="I21" t="s">
+        <v>655</v>
+      </c>
+      <c r="J21" t="s">
+        <v>675</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="676">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -71078,7 +71078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,6 +3057,1069 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J1" t="s">
+        <v>581</v>
+      </c>
+      <c r="K1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L1" t="s">
+        <v>583</v>
+      </c>
+      <c r="M1" t="s">
+        <v>584</v>
+      </c>
+      <c r="N1" t="s">
+        <v>585</v>
+      </c>
+      <c r="O1" t="s">
+        <v>586</v>
+      </c>
+      <c r="P1" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>616</v>
+      </c>
+      <c r="I2" t="s">
+        <v>636</v>
+      </c>
+      <c r="J2" t="s">
+        <v>656</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>617</v>
+      </c>
+      <c r="I3" t="s">
+        <v>637</v>
+      </c>
+      <c r="J3" t="s">
+        <v>657</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>618</v>
+      </c>
+      <c r="I4" t="s">
+        <v>638</v>
+      </c>
+      <c r="J4" t="s">
+        <v>658</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>589</v>
+      </c>
+      <c r="B5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>609</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>619</v>
+      </c>
+      <c r="I5" t="s">
+        <v>639</v>
+      </c>
+      <c r="J5" t="s">
+        <v>659</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>608</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>620</v>
+      </c>
+      <c r="I6" t="s">
+        <v>640</v>
+      </c>
+      <c r="J6" t="s">
+        <v>660</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>590</v>
+      </c>
+      <c r="B7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>606</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>621</v>
+      </c>
+      <c r="I7" t="s">
+        <v>641</v>
+      </c>
+      <c r="J7" t="s">
+        <v>661</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>602</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>622</v>
+      </c>
+      <c r="I8" t="s">
+        <v>642</v>
+      </c>
+      <c r="J8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>591</v>
+      </c>
+      <c r="B9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>615</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>623</v>
+      </c>
+      <c r="I9" t="s">
+        <v>643</v>
+      </c>
+      <c r="J9" t="s">
+        <v>663</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>592</v>
+      </c>
+      <c r="B10" t="s">
+        <v>604</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I10" t="s">
+        <v>644</v>
+      </c>
+      <c r="J10" t="s">
+        <v>664</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B11" t="s">
+        <v>605</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>612</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>625</v>
+      </c>
+      <c r="I11" t="s">
+        <v>645</v>
+      </c>
+      <c r="J11" t="s">
+        <v>665</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>605</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>626</v>
+      </c>
+      <c r="I12" t="s">
+        <v>646</v>
+      </c>
+      <c r="J12" t="s">
+        <v>666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>593</v>
+      </c>
+      <c r="B13" t="s">
+        <v>607</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>603</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>627</v>
+      </c>
+      <c r="I13" t="s">
+        <v>647</v>
+      </c>
+      <c r="J13" t="s">
+        <v>667</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" t="s">
+        <v>608</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>601</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>628</v>
+      </c>
+      <c r="I14" t="s">
+        <v>648</v>
+      </c>
+      <c r="J14" t="s">
+        <v>668</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B15" t="s">
+        <v>609</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>600</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>629</v>
+      </c>
+      <c r="I15" t="s">
+        <v>649</v>
+      </c>
+      <c r="J15" t="s">
+        <v>669</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>596</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>630</v>
+      </c>
+      <c r="I16" t="s">
+        <v>650</v>
+      </c>
+      <c r="J16" t="s">
+        <v>670</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>593</v>
+      </c>
+      <c r="B17" t="s">
+        <v>611</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>602</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>631</v>
+      </c>
+      <c r="I17" t="s">
+        <v>651</v>
+      </c>
+      <c r="J17" t="s">
+        <v>671</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B18" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>599</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>632</v>
+      </c>
+      <c r="I18" t="s">
+        <v>652</v>
+      </c>
+      <c r="J18" t="s">
+        <v>672</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>595</v>
+      </c>
+      <c r="B19" t="s">
+        <v>613</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>597</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>633</v>
+      </c>
+      <c r="I19" t="s">
+        <v>653</v>
+      </c>
+      <c r="J19" t="s">
+        <v>673</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>595</v>
+      </c>
+      <c r="B20" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>634</v>
+      </c>
+      <c r="I20" t="s">
+        <v>654</v>
+      </c>
+      <c r="J20" t="s">
+        <v>674</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B21" t="s">
+        <v>615</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>635</v>
+      </c>
+      <c r="I21" t="s">
+        <v>655</v>
+      </c>
+      <c r="J21" t="s">
+        <v>675</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -71076,1061 +72139,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C1" t="s">
-        <v>574</v>
-      </c>
-      <c r="D1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E1" t="s">
-        <v>576</v>
-      </c>
-      <c r="F1" t="s">
-        <v>577</v>
-      </c>
-      <c r="G1" t="s">
-        <v>578</v>
-      </c>
-      <c r="H1" t="s">
-        <v>579</v>
-      </c>
-      <c r="I1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J1" t="s">
-        <v>581</v>
-      </c>
-      <c r="K1" t="s">
-        <v>582</v>
-      </c>
-      <c r="L1" t="s">
-        <v>583</v>
-      </c>
-      <c r="M1" t="s">
-        <v>584</v>
-      </c>
-      <c r="N1" t="s">
-        <v>585</v>
-      </c>
-      <c r="O1" t="s">
-        <v>586</v>
-      </c>
-      <c r="P1" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I2" t="s">
-        <v>636</v>
-      </c>
-      <c r="J2" t="s">
-        <v>656</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>589</v>
-      </c>
-      <c r="B3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>611</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>617</v>
-      </c>
-      <c r="I3" t="s">
-        <v>637</v>
-      </c>
-      <c r="J3" t="s">
-        <v>657</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>589</v>
-      </c>
-      <c r="B4" t="s">
-        <v>598</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>610</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>618</v>
-      </c>
-      <c r="I4" t="s">
-        <v>638</v>
-      </c>
-      <c r="J4" t="s">
-        <v>658</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>589</v>
-      </c>
-      <c r="B5" t="s">
-        <v>599</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>609</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>619</v>
-      </c>
-      <c r="I5" t="s">
-        <v>639</v>
-      </c>
-      <c r="J5" t="s">
-        <v>659</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>589</v>
-      </c>
-      <c r="B6" t="s">
-        <v>600</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>608</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>620</v>
-      </c>
-      <c r="I6" t="s">
-        <v>640</v>
-      </c>
-      <c r="J6" t="s">
-        <v>660</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>590</v>
-      </c>
-      <c r="B7" t="s">
-        <v>601</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>606</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>621</v>
-      </c>
-      <c r="I7" t="s">
-        <v>641</v>
-      </c>
-      <c r="J7" t="s">
-        <v>661</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>591</v>
-      </c>
-      <c r="B8" t="s">
-        <v>602</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>614</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>622</v>
-      </c>
-      <c r="I8" t="s">
-        <v>642</v>
-      </c>
-      <c r="J8" t="s">
-        <v>662</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>591</v>
-      </c>
-      <c r="B9" t="s">
-        <v>603</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>615</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>623</v>
-      </c>
-      <c r="I9" t="s">
-        <v>643</v>
-      </c>
-      <c r="J9" t="s">
-        <v>663</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>592</v>
-      </c>
-      <c r="B10" t="s">
-        <v>604</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>607</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>624</v>
-      </c>
-      <c r="I10" t="s">
-        <v>644</v>
-      </c>
-      <c r="J10" t="s">
-        <v>664</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>592</v>
-      </c>
-      <c r="B11" t="s">
-        <v>605</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>612</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>625</v>
-      </c>
-      <c r="I11" t="s">
-        <v>645</v>
-      </c>
-      <c r="J11" t="s">
-        <v>665</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B12" t="s">
-        <v>606</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>605</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H12" t="s">
-        <v>626</v>
-      </c>
-      <c r="I12" t="s">
-        <v>646</v>
-      </c>
-      <c r="J12" t="s">
-        <v>666</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>593</v>
-      </c>
-      <c r="B13" t="s">
-        <v>607</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>603</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>627</v>
-      </c>
-      <c r="I13" t="s">
-        <v>647</v>
-      </c>
-      <c r="J13" t="s">
-        <v>667</v>
-      </c>
-      <c r="K13" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>593</v>
-      </c>
-      <c r="B14" t="s">
-        <v>608</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>601</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H14" t="s">
-        <v>628</v>
-      </c>
-      <c r="I14" t="s">
-        <v>648</v>
-      </c>
-      <c r="J14" t="s">
-        <v>668</v>
-      </c>
-      <c r="K14" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.576</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>593</v>
-      </c>
-      <c r="B15" t="s">
-        <v>609</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>600</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H15" t="s">
-        <v>629</v>
-      </c>
-      <c r="I15" t="s">
-        <v>649</v>
-      </c>
-      <c r="J15" t="s">
-        <v>669</v>
-      </c>
-      <c r="K15" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>593</v>
-      </c>
-      <c r="B16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>596</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H16" t="s">
-        <v>630</v>
-      </c>
-      <c r="I16" t="s">
-        <v>650</v>
-      </c>
-      <c r="J16" t="s">
-        <v>670</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>593</v>
-      </c>
-      <c r="B17" t="s">
-        <v>611</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>602</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>631</v>
-      </c>
-      <c r="I17" t="s">
-        <v>651</v>
-      </c>
-      <c r="J17" t="s">
-        <v>671</v>
-      </c>
-      <c r="K17" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.152</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>594</v>
-      </c>
-      <c r="B18" t="s">
-        <v>612</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>599</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H18" t="s">
-        <v>632</v>
-      </c>
-      <c r="I18" t="s">
-        <v>652</v>
-      </c>
-      <c r="J18" t="s">
-        <v>672</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>595</v>
-      </c>
-      <c r="B19" t="s">
-        <v>613</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>597</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>633</v>
-      </c>
-      <c r="I19" t="s">
-        <v>653</v>
-      </c>
-      <c r="J19" t="s">
-        <v>673</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.825</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>595</v>
-      </c>
-      <c r="B20" t="s">
-        <v>614</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>604</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>634</v>
-      </c>
-      <c r="I20" t="s">
-        <v>654</v>
-      </c>
-      <c r="J20" t="s">
-        <v>674</v>
-      </c>
-      <c r="K20" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>595</v>
-      </c>
-      <c r="B21" t="s">
-        <v>615</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>598</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>635</v>
-      </c>
-      <c r="I21" t="s">
-        <v>655</v>
-      </c>
-      <c r="J21" t="s">
-        <v>675</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,7 +3057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
+    <sheet name="Stand2" sheetId="14" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="15"/>
   </sheets>
 </workbook>
 </file>
@@ -3057,7 +3057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="744">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1825,6 +1827,429 @@
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
   </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
+    <t>Roda JC Kerkrade</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>7.99%</t>
+  </si>
+  <si>
+    <t>23.96%</t>
+  </si>
+  <si>
+    <t>1.46%</t>
+  </si>
+  <si>
+    <t>79.94%</t>
+  </si>
+  <si>
+    <t>56.86%</t>
+  </si>
+  <si>
+    <t>64.61%</t>
+  </si>
+  <si>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>31.36%</t>
+  </si>
+  <si>
+    <t>48.76%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>11.92%</t>
+  </si>
+  <si>
+    <t>18.46%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>13.44%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>20.18%</t>
+  </si>
+  <si>
+    <t>33.73%</t>
+  </si>
+  <si>
+    <t>29.36%</t>
+  </si>
+  <si>
+    <t>22.81%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>80.09%</t>
+  </si>
+  <si>
+    <t>57.58%</t>
+  </si>
+  <si>
+    <t>93.44%</t>
+  </si>
+  <si>
+    <t>6.62%</t>
+  </si>
+  <si>
+    <t>18.34%</t>
+  </si>
+  <si>
+    <t>15.21%</t>
+  </si>
+  <si>
+    <t>27.77%</t>
+  </si>
+  <si>
+    <t>39.28%</t>
+  </si>
+  <si>
+    <t>28.43%</t>
+  </si>
 </sst>
 </file>
 
@@ -83128,4 +83553,3281 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P1" t="s">
+        <v>607</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>608</v>
+      </c>
+      <c r="R1" t="s">
+        <v>609</v>
+      </c>
+      <c r="S1" t="s">
+        <v>610</v>
+      </c>
+      <c r="T1" t="s">
+        <v>611</v>
+      </c>
+      <c r="U1" t="s">
+        <v>612</v>
+      </c>
+      <c r="V1" t="s">
+        <v>613</v>
+      </c>
+      <c r="W1" t="s">
+        <v>614</v>
+      </c>
+      <c r="X1" t="s">
+        <v>615</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>616</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>617</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="R2" t="n">
+        <v>87</v>
+      </c>
+      <c r="S2" t="n">
+        <v>54</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.667333333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>29</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.819333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.527</v>
+      </c>
+      <c r="R3" t="n">
+        <v>85</v>
+      </c>
+      <c r="S3" t="n">
+        <v>55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.77966666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17566666666667</v>
+      </c>
+      <c r="V3" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.95533333333333</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R4" t="n">
+        <v>70</v>
+      </c>
+      <c r="S4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R5" t="n">
+        <v>86</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V5" t="n">
+        <v>43</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="R6" t="n">
+        <v>65</v>
+      </c>
+      <c r="S6" t="n">
+        <v>64</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.70766666666667</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="V6" t="n">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>21.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.653666666666667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.333333333333336</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.76166666666667</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R7" t="n">
+        <v>62</v>
+      </c>
+      <c r="S7" t="n">
+        <v>28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V7" t="n">
+        <v>31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="R8" t="n">
+        <v>86</v>
+      </c>
+      <c r="S8" t="n">
+        <v>41</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="V8" t="n">
+        <v>28.6666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73</v>
+      </c>
+      <c r="S9" t="n">
+        <v>103</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.87033333333333</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24.3333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.395333333333333</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.34533333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>58.6666666666667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>49</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="R11" t="n">
+        <v>52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11566666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.00433333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20.6666666666667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.111333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-3.33333333333334</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="R12" t="n">
+        <v>68</v>
+      </c>
+      <c r="S12" t="n">
+        <v>79</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.03933333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="V12" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.305666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.66666666666666</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.38433333333333</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.146</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R13" t="n">
+        <v>75</v>
+      </c>
+      <c r="S13" t="n">
+        <v>38</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="V13" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>19</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.938</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>56.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>93</v>
+      </c>
+      <c r="S14" t="n">
+        <v>122</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.40666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>40.6666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0973333333333328</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-9.66666666666666</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.91066666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>71.6666666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="R15" t="n">
+        <v>60</v>
+      </c>
+      <c r="S15" t="n">
+        <v>46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.6315</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="V15" t="n">
+        <v>30</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.8085</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="R16" t="n">
+        <v>33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.870666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.05366666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11</v>
+      </c>
+      <c r="W16" t="n">
+        <v>34.6666666666667</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.183</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-23.6666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.92433333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.6666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R17" t="n">
+        <v>47</v>
+      </c>
+      <c r="S17" t="n">
+        <v>80</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.15833333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.44333333333333</v>
+      </c>
+      <c r="V17" t="n">
+        <v>15.6666666666667</v>
+      </c>
+      <c r="W17" t="n">
+        <v>26.6666666666667</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.60166666666667</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="R18" t="n">
+        <v>45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>66</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>33</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.336</v>
+      </c>
+      <c r="R19" t="n">
+        <v>38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>61</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="V19" t="n">
+        <v>19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.911</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>46</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="V20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.4045</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.5445</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="V21" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.219</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R22" t="n">
+        <v>14</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="R23" t="n">
+        <v>41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>66</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>33</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D1" t="s">
+        <v>622</v>
+      </c>
+      <c r="E1" t="s">
+        <v>623</v>
+      </c>
+      <c r="F1" t="s">
+        <v>624</v>
+      </c>
+      <c r="G1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J1" t="s">
+        <v>628</v>
+      </c>
+      <c r="K1" t="s">
+        <v>629</v>
+      </c>
+      <c r="L1" t="s">
+        <v>630</v>
+      </c>
+      <c r="M1" t="s">
+        <v>631</v>
+      </c>
+      <c r="N1" t="s">
+        <v>632</v>
+      </c>
+      <c r="O1" t="s">
+        <v>633</v>
+      </c>
+      <c r="P1" t="s">
+        <v>634</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>666</v>
+      </c>
+      <c r="I2" t="s">
+        <v>692</v>
+      </c>
+      <c r="J2" t="s">
+        <v>718</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>659</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>667</v>
+      </c>
+      <c r="I3" t="s">
+        <v>693</v>
+      </c>
+      <c r="J3" t="s">
+        <v>719</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>636</v>
+      </c>
+      <c r="B4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>658</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>668</v>
+      </c>
+      <c r="I4" t="s">
+        <v>694</v>
+      </c>
+      <c r="J4" t="s">
+        <v>720</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>657</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>669</v>
+      </c>
+      <c r="I5" t="s">
+        <v>695</v>
+      </c>
+      <c r="J5" t="s">
+        <v>721</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B6" t="s">
+        <v>648</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>656</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>670</v>
+      </c>
+      <c r="I6" t="s">
+        <v>696</v>
+      </c>
+      <c r="J6" t="s">
+        <v>722</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B7" t="s">
+        <v>649</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>654</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>671</v>
+      </c>
+      <c r="I7" t="s">
+        <v>697</v>
+      </c>
+      <c r="J7" t="s">
+        <v>723</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>662</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>672</v>
+      </c>
+      <c r="I8" t="s">
+        <v>698</v>
+      </c>
+      <c r="J8" t="s">
+        <v>724</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>638</v>
+      </c>
+      <c r="B9" t="s">
+        <v>651</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>663</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>673</v>
+      </c>
+      <c r="I9" t="s">
+        <v>699</v>
+      </c>
+      <c r="J9" t="s">
+        <v>725</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>639</v>
+      </c>
+      <c r="B10" t="s">
+        <v>652</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>655</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>674</v>
+      </c>
+      <c r="I10" t="s">
+        <v>700</v>
+      </c>
+      <c r="J10" t="s">
+        <v>726</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>639</v>
+      </c>
+      <c r="B11" t="s">
+        <v>653</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>660</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>675</v>
+      </c>
+      <c r="I11" t="s">
+        <v>701</v>
+      </c>
+      <c r="J11" t="s">
+        <v>727</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>640</v>
+      </c>
+      <c r="B12" t="s">
+        <v>654</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>653</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>676</v>
+      </c>
+      <c r="I12" t="s">
+        <v>702</v>
+      </c>
+      <c r="J12" t="s">
+        <v>728</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>640</v>
+      </c>
+      <c r="B13" t="s">
+        <v>655</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>651</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>677</v>
+      </c>
+      <c r="I13" t="s">
+        <v>703</v>
+      </c>
+      <c r="J13" t="s">
+        <v>729</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>640</v>
+      </c>
+      <c r="B14" t="s">
+        <v>656</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>649</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>678</v>
+      </c>
+      <c r="I14" t="s">
+        <v>704</v>
+      </c>
+      <c r="J14" t="s">
+        <v>730</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>640</v>
+      </c>
+      <c r="B15" t="s">
+        <v>657</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>648</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>679</v>
+      </c>
+      <c r="I15" t="s">
+        <v>705</v>
+      </c>
+      <c r="J15" t="s">
+        <v>731</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>640</v>
+      </c>
+      <c r="B16" t="s">
+        <v>658</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>644</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>680</v>
+      </c>
+      <c r="I16" t="s">
+        <v>706</v>
+      </c>
+      <c r="J16" t="s">
+        <v>732</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>640</v>
+      </c>
+      <c r="B17" t="s">
+        <v>659</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>650</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>681</v>
+      </c>
+      <c r="I17" t="s">
+        <v>707</v>
+      </c>
+      <c r="J17" t="s">
+        <v>733</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>641</v>
+      </c>
+      <c r="B18" t="s">
+        <v>660</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>647</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>682</v>
+      </c>
+      <c r="I18" t="s">
+        <v>708</v>
+      </c>
+      <c r="J18" t="s">
+        <v>734</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>642</v>
+      </c>
+      <c r="B19" t="s">
+        <v>661</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>645</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>683</v>
+      </c>
+      <c r="I19" t="s">
+        <v>709</v>
+      </c>
+      <c r="J19" t="s">
+        <v>735</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>642</v>
+      </c>
+      <c r="B20" t="s">
+        <v>662</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>652</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>684</v>
+      </c>
+      <c r="I20" t="s">
+        <v>710</v>
+      </c>
+      <c r="J20" t="s">
+        <v>736</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>642</v>
+      </c>
+      <c r="B21" t="s">
+        <v>663</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>646</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>685</v>
+      </c>
+      <c r="I21" t="s">
+        <v>711</v>
+      </c>
+      <c r="J21" t="s">
+        <v>737</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>643</v>
+      </c>
+      <c r="B22" t="s">
+        <v>649</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>655</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>686</v>
+      </c>
+      <c r="I22" t="s">
+        <v>712</v>
+      </c>
+      <c r="J22" t="s">
+        <v>738</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>643</v>
+      </c>
+      <c r="B23" t="s">
+        <v>644</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>665</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>687</v>
+      </c>
+      <c r="I23" t="s">
+        <v>713</v>
+      </c>
+      <c r="J23" t="s">
+        <v>739</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>643</v>
+      </c>
+      <c r="B24" t="s">
+        <v>645</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>652</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>688</v>
+      </c>
+      <c r="I24" t="s">
+        <v>714</v>
+      </c>
+      <c r="J24" t="s">
+        <v>740</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B25" t="s">
+        <v>650</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>658</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>689</v>
+      </c>
+      <c r="I25" t="s">
+        <v>715</v>
+      </c>
+      <c r="J25" t="s">
+        <v>741</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>643</v>
+      </c>
+      <c r="B26" t="s">
+        <v>664</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>660</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>690</v>
+      </c>
+      <c r="I26" t="s">
+        <v>716</v>
+      </c>
+      <c r="J26" t="s">
+        <v>742</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>643</v>
+      </c>
+      <c r="B27" t="s">
+        <v>646</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>654</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>691</v>
+      </c>
+      <c r="I27" t="s">
+        <v>717</v>
+      </c>
+      <c r="J27" t="s">
+        <v>743</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="755">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1846,6 +1848,441 @@
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
   </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
+    <t>Roda JC Kerkrade</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>7.99%</t>
+  </si>
+  <si>
+    <t>23.96%</t>
+  </si>
+  <si>
+    <t>1.46%</t>
+  </si>
+  <si>
+    <t>79.94%</t>
+  </si>
+  <si>
+    <t>56.86%</t>
+  </si>
+  <si>
+    <t>64.61%</t>
+  </si>
+  <si>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>31.36%</t>
+  </si>
+  <si>
+    <t>48.76%</t>
+  </si>
+  <si>
+    <t>58.04%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>11.92%</t>
+  </si>
+  <si>
+    <t>18.46%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>13.44%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>20.18%</t>
+  </si>
+  <si>
+    <t>33.73%</t>
+  </si>
+  <si>
+    <t>29.36%</t>
+  </si>
+  <si>
+    <t>22.81%</t>
+  </si>
+  <si>
+    <t>21.06%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>80.09%</t>
+  </si>
+  <si>
+    <t>57.58%</t>
+  </si>
+  <si>
+    <t>93.44%</t>
+  </si>
+  <si>
+    <t>6.62%</t>
+  </si>
+  <si>
+    <t>18.34%</t>
+  </si>
+  <si>
+    <t>15.21%</t>
+  </si>
+  <si>
+    <t>27.77%</t>
+  </si>
+  <si>
+    <t>39.28%</t>
+  </si>
+  <si>
+    <t>28.43%</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
 </sst>
 </file>
 
@@ -85687,4 +86124,3328 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P1" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>615</v>
+      </c>
+      <c r="R1" t="s">
+        <v>616</v>
+      </c>
+      <c r="S1" t="s">
+        <v>617</v>
+      </c>
+      <c r="T1" t="s">
+        <v>618</v>
+      </c>
+      <c r="U1" t="s">
+        <v>619</v>
+      </c>
+      <c r="V1" t="s">
+        <v>620</v>
+      </c>
+      <c r="W1" t="s">
+        <v>621</v>
+      </c>
+      <c r="X1" t="s">
+        <v>622</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>623</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>624</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="R2" t="n">
+        <v>87</v>
+      </c>
+      <c r="S2" t="n">
+        <v>54</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.667333333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>29</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.819333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.527</v>
+      </c>
+      <c r="R3" t="n">
+        <v>85</v>
+      </c>
+      <c r="S3" t="n">
+        <v>55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.77966666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17566666666667</v>
+      </c>
+      <c r="V3" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.95533333333333</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.361</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="R4" t="n">
+        <v>117</v>
+      </c>
+      <c r="S4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12033333333333</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.996333333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.11666666666667</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55.3333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R5" t="n">
+        <v>70</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V5" t="n">
+        <v>35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R6" t="n">
+        <v>86</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>43</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.70766666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.3333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.653666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.333333333333336</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.76166666666667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V8" t="n">
+        <v>31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>86</v>
+      </c>
+      <c r="S9" t="n">
+        <v>41</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="V9" t="n">
+        <v>28.6666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>49</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="R11" t="n">
+        <v>73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>103</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.87033333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.3333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.395333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.34533333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>58.6666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="R12" t="n">
+        <v>52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11566666666667</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.00433333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20.6666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.111333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.33333333333334</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.03933333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="V13" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.305666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-3.66666666666666</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.38433333333333</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R14" t="n">
+        <v>93</v>
+      </c>
+      <c r="S14" t="n">
+        <v>122</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.40666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>40.6666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0973333333333328</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-9.66666666666666</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.91066666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>71.6666666666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="R15" t="n">
+        <v>60</v>
+      </c>
+      <c r="S15" t="n">
+        <v>46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.6315</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="V15" t="n">
+        <v>30</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.8085</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="R16" t="n">
+        <v>33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.870666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.05366666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11</v>
+      </c>
+      <c r="W16" t="n">
+        <v>34.6666666666667</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.183</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-23.6666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.92433333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.6666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="R17" t="n">
+        <v>49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>103</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.744333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.85033333333333</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.59466666666667</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50.6666666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R18" t="n">
+        <v>47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>80</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.15833333333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44333333333333</v>
+      </c>
+      <c r="V18" t="n">
+        <v>15.6666666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>26.6666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.60166666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="R19" t="n">
+        <v>45</v>
+      </c>
+      <c r="S19" t="n">
+        <v>66</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>33</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>46</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="V20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>23</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.4045</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.5445</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="V21" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" t="n">
+        <v>15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.219</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R22" t="n">
+        <v>14</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V22" t="n">
+        <v>14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>24</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.716</v>
+      </c>
+      <c r="R23" t="n">
+        <v>41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>66</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="V23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>33</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.275</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C1" t="s">
+        <v>628</v>
+      </c>
+      <c r="D1" t="s">
+        <v>629</v>
+      </c>
+      <c r="E1" t="s">
+        <v>630</v>
+      </c>
+      <c r="F1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G1" t="s">
+        <v>632</v>
+      </c>
+      <c r="H1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I1" t="s">
+        <v>634</v>
+      </c>
+      <c r="J1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K1" t="s">
+        <v>636</v>
+      </c>
+      <c r="L1" t="s">
+        <v>637</v>
+      </c>
+      <c r="M1" t="s">
+        <v>638</v>
+      </c>
+      <c r="N1" t="s">
+        <v>639</v>
+      </c>
+      <c r="O1" t="s">
+        <v>640</v>
+      </c>
+      <c r="P1" t="s">
+        <v>641</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>674</v>
+      </c>
+      <c r="I2" t="s">
+        <v>701</v>
+      </c>
+      <c r="J2" t="s">
+        <v>728</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>675</v>
+      </c>
+      <c r="I3" t="s">
+        <v>702</v>
+      </c>
+      <c r="J3" t="s">
+        <v>729</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>666</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>676</v>
+      </c>
+      <c r="I4" t="s">
+        <v>703</v>
+      </c>
+      <c r="J4" t="s">
+        <v>730</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>643</v>
+      </c>
+      <c r="B5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>665</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>677</v>
+      </c>
+      <c r="I5" t="s">
+        <v>704</v>
+      </c>
+      <c r="J5" t="s">
+        <v>731</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B6" t="s">
+        <v>656</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>664</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>678</v>
+      </c>
+      <c r="I6" t="s">
+        <v>705</v>
+      </c>
+      <c r="J6" t="s">
+        <v>732</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>644</v>
+      </c>
+      <c r="B7" t="s">
+        <v>657</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>662</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>679</v>
+      </c>
+      <c r="I7" t="s">
+        <v>706</v>
+      </c>
+      <c r="J7" t="s">
+        <v>733</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" t="s">
+        <v>658</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>670</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>680</v>
+      </c>
+      <c r="I8" t="s">
+        <v>707</v>
+      </c>
+      <c r="J8" t="s">
+        <v>734</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>645</v>
+      </c>
+      <c r="B9" t="s">
+        <v>659</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>671</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>681</v>
+      </c>
+      <c r="I9" t="s">
+        <v>708</v>
+      </c>
+      <c r="J9" t="s">
+        <v>735</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>646</v>
+      </c>
+      <c r="B10" t="s">
+        <v>660</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>663</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>682</v>
+      </c>
+      <c r="I10" t="s">
+        <v>709</v>
+      </c>
+      <c r="J10" t="s">
+        <v>736</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>646</v>
+      </c>
+      <c r="B11" t="s">
+        <v>661</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>668</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>683</v>
+      </c>
+      <c r="I11" t="s">
+        <v>710</v>
+      </c>
+      <c r="J11" t="s">
+        <v>737</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B12" t="s">
+        <v>662</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>661</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>684</v>
+      </c>
+      <c r="I12" t="s">
+        <v>711</v>
+      </c>
+      <c r="J12" t="s">
+        <v>738</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>647</v>
+      </c>
+      <c r="B13" t="s">
+        <v>663</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>659</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>685</v>
+      </c>
+      <c r="I13" t="s">
+        <v>712</v>
+      </c>
+      <c r="J13" t="s">
+        <v>739</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>647</v>
+      </c>
+      <c r="B14" t="s">
+        <v>664</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>657</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>686</v>
+      </c>
+      <c r="I14" t="s">
+        <v>713</v>
+      </c>
+      <c r="J14" t="s">
+        <v>740</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>647</v>
+      </c>
+      <c r="B15" t="s">
+        <v>665</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>656</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>687</v>
+      </c>
+      <c r="I15" t="s">
+        <v>714</v>
+      </c>
+      <c r="J15" t="s">
+        <v>741</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B16" t="s">
+        <v>666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>688</v>
+      </c>
+      <c r="I16" t="s">
+        <v>715</v>
+      </c>
+      <c r="J16" t="s">
+        <v>742</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>647</v>
+      </c>
+      <c r="B17" t="s">
+        <v>667</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>658</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>689</v>
+      </c>
+      <c r="I17" t="s">
+        <v>716</v>
+      </c>
+      <c r="J17" t="s">
+        <v>743</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>648</v>
+      </c>
+      <c r="B18" t="s">
+        <v>668</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>655</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>690</v>
+      </c>
+      <c r="I18" t="s">
+        <v>717</v>
+      </c>
+      <c r="J18" t="s">
+        <v>744</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>649</v>
+      </c>
+      <c r="B19" t="s">
+        <v>669</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>653</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>691</v>
+      </c>
+      <c r="I19" t="s">
+        <v>718</v>
+      </c>
+      <c r="J19" t="s">
+        <v>745</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>649</v>
+      </c>
+      <c r="B20" t="s">
+        <v>670</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>660</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>692</v>
+      </c>
+      <c r="I20" t="s">
+        <v>719</v>
+      </c>
+      <c r="J20" t="s">
+        <v>746</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>649</v>
+      </c>
+      <c r="B21" t="s">
+        <v>671</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>654</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>693</v>
+      </c>
+      <c r="I21" t="s">
+        <v>720</v>
+      </c>
+      <c r="J21" t="s">
+        <v>747</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>650</v>
+      </c>
+      <c r="B22" t="s">
+        <v>657</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>663</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>694</v>
+      </c>
+      <c r="I22" t="s">
+        <v>721</v>
+      </c>
+      <c r="J22" t="s">
+        <v>748</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>650</v>
+      </c>
+      <c r="B23" t="s">
+        <v>652</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>673</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>695</v>
+      </c>
+      <c r="I23" t="s">
+        <v>722</v>
+      </c>
+      <c r="J23" t="s">
+        <v>749</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>650</v>
+      </c>
+      <c r="B24" t="s">
+        <v>653</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>660</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>696</v>
+      </c>
+      <c r="I24" t="s">
+        <v>723</v>
+      </c>
+      <c r="J24" t="s">
+        <v>750</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>650</v>
+      </c>
+      <c r="B25" t="s">
+        <v>658</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>666</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>697</v>
+      </c>
+      <c r="I25" t="s">
+        <v>724</v>
+      </c>
+      <c r="J25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>650</v>
+      </c>
+      <c r="B26" t="s">
+        <v>672</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>668</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>698</v>
+      </c>
+      <c r="I26" t="s">
+        <v>725</v>
+      </c>
+      <c r="J26" t="s">
+        <v>752</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>650</v>
+      </c>
+      <c r="B27" t="s">
+        <v>654</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>662</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>699</v>
+      </c>
+      <c r="I27" t="s">
+        <v>726</v>
+      </c>
+      <c r="J27" t="s">
+        <v>753</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>651</v>
+      </c>
+      <c r="B28" t="s">
+        <v>665</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>669</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>700</v>
+      </c>
+      <c r="I28" t="s">
+        <v>727</v>
+      </c>
+      <c r="J28" t="s">
+        <v>754</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="768">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1873,6 +1875,453 @@
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
   </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
+    <t>Roda JC Kerkrade</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>7.99%</t>
+  </si>
+  <si>
+    <t>23.96%</t>
+  </si>
+  <si>
+    <t>1.46%</t>
+  </si>
+  <si>
+    <t>79.94%</t>
+  </si>
+  <si>
+    <t>56.86%</t>
+  </si>
+  <si>
+    <t>64.61%</t>
+  </si>
+  <si>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>31.36%</t>
+  </si>
+  <si>
+    <t>48.76%</t>
+  </si>
+  <si>
+    <t>58.04%</t>
+  </si>
+  <si>
+    <t>46.97%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>11.92%</t>
+  </si>
+  <si>
+    <t>18.46%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>13.44%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>20.18%</t>
+  </si>
+  <si>
+    <t>33.73%</t>
+  </si>
+  <si>
+    <t>29.36%</t>
+  </si>
+  <si>
+    <t>22.81%</t>
+  </si>
+  <si>
+    <t>21.06%</t>
+  </si>
+  <si>
+    <t>24.48%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>80.09%</t>
+  </si>
+  <si>
+    <t>57.58%</t>
+  </si>
+  <si>
+    <t>93.44%</t>
+  </si>
+  <si>
+    <t>6.62%</t>
+  </si>
+  <si>
+    <t>18.34%</t>
+  </si>
+  <si>
+    <t>15.21%</t>
+  </si>
+  <si>
+    <t>27.77%</t>
+  </si>
+  <si>
+    <t>39.28%</t>
+  </si>
+  <si>
+    <t>28.43%</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>28.55%</t>
+  </si>
 </sst>
 </file>
 
@@ -87983,4 +88432,3375 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O1" t="s">
+        <v>140</v>
+      </c>
+      <c r="P1" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>624</v>
+      </c>
+      <c r="R1" t="s">
+        <v>625</v>
+      </c>
+      <c r="S1" t="s">
+        <v>626</v>
+      </c>
+      <c r="T1" t="s">
+        <v>627</v>
+      </c>
+      <c r="U1" t="s">
+        <v>628</v>
+      </c>
+      <c r="V1" t="s">
+        <v>629</v>
+      </c>
+      <c r="W1" t="s">
+        <v>630</v>
+      </c>
+      <c r="X1" t="s">
+        <v>631</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>632</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>633</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="R2" t="n">
+        <v>87</v>
+      </c>
+      <c r="S2" t="n">
+        <v>54</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.48666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.667333333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>29</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.819333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.527</v>
+      </c>
+      <c r="R3" t="n">
+        <v>85</v>
+      </c>
+      <c r="S3" t="n">
+        <v>55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.77966666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17566666666667</v>
+      </c>
+      <c r="V3" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18.3333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.95533333333333</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.361</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="R4" t="n">
+        <v>117</v>
+      </c>
+      <c r="S4" t="n">
+        <v>49</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12033333333333</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.996333333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.11666666666667</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55.3333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.073</v>
+      </c>
+      <c r="R5" t="n">
+        <v>70</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.1985</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5365</v>
+      </c>
+      <c r="V5" t="n">
+        <v>35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R6" t="n">
+        <v>86</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>43</v>
+      </c>
+      <c r="W6" t="n">
+        <v>15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.70766666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.3333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.653666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.333333333333336</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.76166666666667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V8" t="n">
+        <v>31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>86</v>
+      </c>
+      <c r="S9" t="n">
+        <v>41</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="V9" t="n">
+        <v>28.6666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>49</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="R11" t="n">
+        <v>73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>103</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.87033333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.3333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.395333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.34533333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>58.6666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="R12" t="n">
+        <v>52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11566666666667</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.00433333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20.6666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.111333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.33333333333334</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.03933333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="V13" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.305666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-3.66666666666666</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.38433333333333</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.589</v>
+      </c>
+      <c r="R14" t="n">
+        <v>79</v>
+      </c>
+      <c r="S14" t="n">
+        <v>71</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.54133333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.19633333333333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="W14" t="n">
+        <v>23.6666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.66666666666666</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.73766666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R15" t="n">
+        <v>93</v>
+      </c>
+      <c r="S15" t="n">
+        <v>122</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.40666666666667</v>
+      </c>
+      <c r="V15" t="n">
+        <v>31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>40.6666666666667</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0973333333333328</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-9.66666666666666</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.91066666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>71.6666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="R16" t="n">
+        <v>33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>104</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.870666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.05366666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11</v>
+      </c>
+      <c r="W16" t="n">
+        <v>34.6666666666667</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.183</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-23.6666666666667</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.92433333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>45.6666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="R17" t="n">
+        <v>49</v>
+      </c>
+      <c r="S17" t="n">
+        <v>103</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.744333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.85033333333333</v>
+      </c>
+      <c r="V17" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.59466666666667</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50.6666666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.069</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.077</v>
+      </c>
+      <c r="R18" t="n">
+        <v>66</v>
+      </c>
+      <c r="S18" t="n">
+        <v>85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.35633333333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.69233333333333</v>
+      </c>
+      <c r="V18" t="n">
+        <v>22</v>
+      </c>
+      <c r="W18" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.336</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-6.33333333333333</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.04866666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>50.3333333333333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R19" t="n">
+        <v>47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>80</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.15833333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44333333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>15.6666666666667</v>
+      </c>
+      <c r="W19" t="n">
+        <v>26.6666666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.60166666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.072</v>
+      </c>
+      <c r="R20" t="n">
+        <v>45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>66</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="V20" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>33</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.904</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.168</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="R21" t="n">
+        <v>39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>46</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="V21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>23</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.4045</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.5445</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="V22" t="n">
+        <v>13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.219</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R23" t="n">
+        <v>14</v>
+      </c>
+      <c r="S23" t="n">
+        <v>24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V23" t="n">
+        <v>14</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D1" t="s">
+        <v>638</v>
+      </c>
+      <c r="E1" t="s">
+        <v>639</v>
+      </c>
+      <c r="F1" t="s">
+        <v>640</v>
+      </c>
+      <c r="G1" t="s">
+        <v>641</v>
+      </c>
+      <c r="H1" t="s">
+        <v>642</v>
+      </c>
+      <c r="I1" t="s">
+        <v>643</v>
+      </c>
+      <c r="J1" t="s">
+        <v>644</v>
+      </c>
+      <c r="K1" t="s">
+        <v>645</v>
+      </c>
+      <c r="L1" t="s">
+        <v>646</v>
+      </c>
+      <c r="M1" t="s">
+        <v>647</v>
+      </c>
+      <c r="N1" t="s">
+        <v>648</v>
+      </c>
+      <c r="O1" t="s">
+        <v>649</v>
+      </c>
+      <c r="P1" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>684</v>
+      </c>
+      <c r="I2" t="s">
+        <v>712</v>
+      </c>
+      <c r="J2" t="s">
+        <v>740</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>685</v>
+      </c>
+      <c r="I3" t="s">
+        <v>713</v>
+      </c>
+      <c r="J3" t="s">
+        <v>741</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B4" t="s">
+        <v>664</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>676</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>686</v>
+      </c>
+      <c r="I4" t="s">
+        <v>714</v>
+      </c>
+      <c r="J4" t="s">
+        <v>742</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>687</v>
+      </c>
+      <c r="I5" t="s">
+        <v>715</v>
+      </c>
+      <c r="J5" t="s">
+        <v>743</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B6" t="s">
+        <v>666</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>674</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>688</v>
+      </c>
+      <c r="I6" t="s">
+        <v>716</v>
+      </c>
+      <c r="J6" t="s">
+        <v>744</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>653</v>
+      </c>
+      <c r="B7" t="s">
+        <v>667</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>672</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>689</v>
+      </c>
+      <c r="I7" t="s">
+        <v>717</v>
+      </c>
+      <c r="J7" t="s">
+        <v>745</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>654</v>
+      </c>
+      <c r="B8" t="s">
+        <v>668</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>680</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>690</v>
+      </c>
+      <c r="I8" t="s">
+        <v>718</v>
+      </c>
+      <c r="J8" t="s">
+        <v>746</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>654</v>
+      </c>
+      <c r="B9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>681</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>691</v>
+      </c>
+      <c r="I9" t="s">
+        <v>719</v>
+      </c>
+      <c r="J9" t="s">
+        <v>747</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" t="s">
+        <v>670</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>673</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>692</v>
+      </c>
+      <c r="I10" t="s">
+        <v>720</v>
+      </c>
+      <c r="J10" t="s">
+        <v>748</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B11" t="s">
+        <v>671</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>678</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>693</v>
+      </c>
+      <c r="I11" t="s">
+        <v>721</v>
+      </c>
+      <c r="J11" t="s">
+        <v>749</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>656</v>
+      </c>
+      <c r="B12" t="s">
+        <v>672</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>671</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>694</v>
+      </c>
+      <c r="I12" t="s">
+        <v>722</v>
+      </c>
+      <c r="J12" t="s">
+        <v>750</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>656</v>
+      </c>
+      <c r="B13" t="s">
+        <v>673</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>669</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>695</v>
+      </c>
+      <c r="I13" t="s">
+        <v>723</v>
+      </c>
+      <c r="J13" t="s">
+        <v>751</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>656</v>
+      </c>
+      <c r="B14" t="s">
+        <v>674</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>667</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>696</v>
+      </c>
+      <c r="I14" t="s">
+        <v>724</v>
+      </c>
+      <c r="J14" t="s">
+        <v>752</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>656</v>
+      </c>
+      <c r="B15" t="s">
+        <v>675</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>666</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>697</v>
+      </c>
+      <c r="I15" t="s">
+        <v>725</v>
+      </c>
+      <c r="J15" t="s">
+        <v>753</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>656</v>
+      </c>
+      <c r="B16" t="s">
+        <v>676</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>662</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>698</v>
+      </c>
+      <c r="I16" t="s">
+        <v>726</v>
+      </c>
+      <c r="J16" t="s">
+        <v>754</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>656</v>
+      </c>
+      <c r="B17" t="s">
+        <v>677</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>668</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>699</v>
+      </c>
+      <c r="I17" t="s">
+        <v>727</v>
+      </c>
+      <c r="J17" t="s">
+        <v>755</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>657</v>
+      </c>
+      <c r="B18" t="s">
+        <v>678</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>665</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>700</v>
+      </c>
+      <c r="I18" t="s">
+        <v>728</v>
+      </c>
+      <c r="J18" t="s">
+        <v>756</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>658</v>
+      </c>
+      <c r="B19" t="s">
+        <v>679</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>663</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>701</v>
+      </c>
+      <c r="I19" t="s">
+        <v>729</v>
+      </c>
+      <c r="J19" t="s">
+        <v>757</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>658</v>
+      </c>
+      <c r="B20" t="s">
+        <v>680</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>670</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>702</v>
+      </c>
+      <c r="I20" t="s">
+        <v>730</v>
+      </c>
+      <c r="J20" t="s">
+        <v>758</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>658</v>
+      </c>
+      <c r="B21" t="s">
+        <v>681</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>664</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>703</v>
+      </c>
+      <c r="I21" t="s">
+        <v>731</v>
+      </c>
+      <c r="J21" t="s">
+        <v>759</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>659</v>
+      </c>
+      <c r="B22" t="s">
+        <v>667</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>673</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>704</v>
+      </c>
+      <c r="I22" t="s">
+        <v>732</v>
+      </c>
+      <c r="J22" t="s">
+        <v>760</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>659</v>
+      </c>
+      <c r="B23" t="s">
+        <v>662</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>683</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>705</v>
+      </c>
+      <c r="I23" t="s">
+        <v>733</v>
+      </c>
+      <c r="J23" t="s">
+        <v>761</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>659</v>
+      </c>
+      <c r="B24" t="s">
+        <v>663</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>670</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>706</v>
+      </c>
+      <c r="I24" t="s">
+        <v>734</v>
+      </c>
+      <c r="J24" t="s">
+        <v>762</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>659</v>
+      </c>
+      <c r="B25" t="s">
+        <v>668</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>676</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>707</v>
+      </c>
+      <c r="I25" t="s">
+        <v>735</v>
+      </c>
+      <c r="J25" t="s">
+        <v>763</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B26" t="s">
+        <v>682</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>678</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>708</v>
+      </c>
+      <c r="I26" t="s">
+        <v>736</v>
+      </c>
+      <c r="J26" t="s">
+        <v>764</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>659</v>
+      </c>
+      <c r="B27" t="s">
+        <v>664</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>672</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>709</v>
+      </c>
+      <c r="I27" t="s">
+        <v>737</v>
+      </c>
+      <c r="J27" t="s">
+        <v>765</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>660</v>
+      </c>
+      <c r="B28" t="s">
+        <v>675</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>679</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>710</v>
+      </c>
+      <c r="I28" t="s">
+        <v>738</v>
+      </c>
+      <c r="J28" t="s">
+        <v>766</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>661</v>
+      </c>
+      <c r="B29" t="s">
+        <v>666</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>680</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>711</v>
+      </c>
+      <c r="I29" t="s">
+        <v>739</v>
+      </c>
+      <c r="J29" t="s">
+        <v>767</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -1918,6 +1920,474 @@
   <si>
     <t xml:space="preserve">VVV Venlo - Heracles Almelo</t>
   </si>
+  <si>
+    <t xml:space="preserve">box_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xt_away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_for.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box_against.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.difference.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.diff.90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xT.total..90min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box.total..90min</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>HomeName</t>
+  </si>
+  <si>
+    <t>HomeGoals</t>
+  </si>
+  <si>
+    <t>AwayGoals</t>
+  </si>
+  <si>
+    <t>AwayName</t>
+  </si>
+  <si>
+    <t>Home_xG</t>
+  </si>
+  <si>
+    <t>Away_xG</t>
+  </si>
+  <si>
+    <t>home_win_prob</t>
+  </si>
+  <si>
+    <t>draw_prob</t>
+  </si>
+  <si>
+    <t>away_win_prob</t>
+  </si>
+  <si>
+    <t>box_home</t>
+  </si>
+  <si>
+    <t>box_away</t>
+  </si>
+  <si>
+    <t>xt_home</t>
+  </si>
+  <si>
+    <t>xt_away</t>
+  </si>
+  <si>
+    <t>home_odds</t>
+  </si>
+  <si>
+    <t>draw_odds</t>
+  </si>
+  <si>
+    <t>away_odds</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>FC Dordrecht</t>
+  </si>
+  <si>
+    <t>FC Emmen</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>TOP Oss</t>
+  </si>
+  <si>
+    <t>VVV Venlo</t>
+  </si>
+  <si>
+    <t>FC Den Bosch</t>
+  </si>
+  <si>
+    <t>Helmond Sport</t>
+  </si>
+  <si>
+    <t>MVV</t>
+  </si>
+  <si>
+    <t>AZ II</t>
+  </si>
+  <si>
+    <t>PSV II</t>
+  </si>
+  <si>
+    <t>Almere City FC</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>Heracles Almelo</t>
+  </si>
+  <si>
+    <t>NAC Breda</t>
+  </si>
+  <si>
+    <t>RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Roda JC</t>
+  </si>
+  <si>
+    <t>FC Volendam</t>
+  </si>
+  <si>
+    <t>Ajax II</t>
+  </si>
+  <si>
+    <t>De Graafschap</t>
+  </si>
+  <si>
+    <t>FC Utrecht II</t>
+  </si>
+  <si>
+    <t>MVV Maastricht</t>
+  </si>
+  <si>
+    <t>Roda JC Kerkrade</t>
+  </si>
+  <si>
+    <t>39.79%</t>
+  </si>
+  <si>
+    <t>27.39%</t>
+  </si>
+  <si>
+    <t>27.04%</t>
+  </si>
+  <si>
+    <t>38.22%</t>
+  </si>
+  <si>
+    <t>3.02%</t>
+  </si>
+  <si>
+    <t>25.27%</t>
+  </si>
+  <si>
+    <t>29.68%</t>
+  </si>
+  <si>
+    <t>42.21%</t>
+  </si>
+  <si>
+    <t>26.53%</t>
+  </si>
+  <si>
+    <t>92.43%</t>
+  </si>
+  <si>
+    <t>16.99%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>71.36%</t>
+  </si>
+  <si>
+    <t>71.46%</t>
+  </si>
+  <si>
+    <t>35.69%</t>
+  </si>
+  <si>
+    <t>96.19%</t>
+  </si>
+  <si>
+    <t>74.68%</t>
+  </si>
+  <si>
+    <t>7.99%</t>
+  </si>
+  <si>
+    <t>23.96%</t>
+  </si>
+  <si>
+    <t>1.46%</t>
+  </si>
+  <si>
+    <t>79.94%</t>
+  </si>
+  <si>
+    <t>56.86%</t>
+  </si>
+  <si>
+    <t>64.61%</t>
+  </si>
+  <si>
+    <t>38.5%</t>
+  </si>
+  <si>
+    <t>31.36%</t>
+  </si>
+  <si>
+    <t>48.76%</t>
+  </si>
+  <si>
+    <t>58.04%</t>
+  </si>
+  <si>
+    <t>46.97%</t>
+  </si>
+  <si>
+    <t>18.33%</t>
+  </si>
+  <si>
+    <t>30.53%</t>
+  </si>
+  <si>
+    <t>25.13%</t>
+  </si>
+  <si>
+    <t>31.48%</t>
+  </si>
+  <si>
+    <t>25.19%</t>
+  </si>
+  <si>
+    <t>20.28%</t>
+  </si>
+  <si>
+    <t>5.98%</t>
+  </si>
+  <si>
+    <t>20.88%</t>
+  </si>
+  <si>
+    <t>22.15%</t>
+  </si>
+  <si>
+    <t>26.01%</t>
+  </si>
+  <si>
+    <t>36.66%</t>
+  </si>
+  <si>
+    <t>6.52%</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>11.17%</t>
+  </si>
+  <si>
+    <t>14.75%</t>
+  </si>
+  <si>
+    <t>17.74%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>3.28%</t>
+  </si>
+  <si>
+    <t>15.78%</t>
+  </si>
+  <si>
+    <t>11.92%</t>
+  </si>
+  <si>
+    <t>18.46%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>13.44%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>20.18%</t>
+  </si>
+  <si>
+    <t>33.73%</t>
+  </si>
+  <si>
+    <t>29.36%</t>
+  </si>
+  <si>
+    <t>22.81%</t>
+  </si>
+  <si>
+    <t>21.06%</t>
+  </si>
+  <si>
+    <t>24.48%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>23.16%</t>
+  </si>
+  <si>
+    <t>35.08%</t>
+  </si>
+  <si>
+    <t>41.13%</t>
+  </si>
+  <si>
+    <t>47.77%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>53.85%</t>
+  </si>
+  <si>
+    <t>48.17%</t>
+  </si>
+  <si>
+    <t>31.78%</t>
+  </si>
+  <si>
+    <t>36.81%</t>
+  </si>
+  <si>
+    <t>1.05%</t>
+  </si>
+  <si>
+    <t>61.41%</t>
+  </si>
+  <si>
+    <t>82.33%</t>
+  </si>
+  <si>
+    <t>13.89%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>33.91%</t>
+  </si>
+  <si>
+    <t>0.53%</t>
+  </si>
+  <si>
+    <t>9.54%</t>
+  </si>
+  <si>
+    <t>80.09%</t>
+  </si>
+  <si>
+    <t>57.58%</t>
+  </si>
+  <si>
+    <t>93.44%</t>
+  </si>
+  <si>
+    <t>6.62%</t>
+  </si>
+  <si>
+    <t>18.34%</t>
+  </si>
+  <si>
+    <t>15.21%</t>
+  </si>
+  <si>
+    <t>27.77%</t>
+  </si>
+  <si>
+    <t>39.28%</t>
+  </si>
+  <si>
+    <t>28.43%</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>28.55%</t>
+  </si>
+  <si>
+    <t>62.47%</t>
+  </si>
+  <si>
+    <t>46.31%</t>
+  </si>
 </sst>
 </file>
 
@@ -92985,4 +93455,3528 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O1" t="s">
+        <v>147</v>
+      </c>
+      <c r="P1" t="s">
+        <v>638</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>639</v>
+      </c>
+      <c r="R1" t="s">
+        <v>640</v>
+      </c>
+      <c r="S1" t="s">
+        <v>641</v>
+      </c>
+      <c r="T1" t="s">
+        <v>642</v>
+      </c>
+      <c r="U1" t="s">
+        <v>643</v>
+      </c>
+      <c r="V1" t="s">
+        <v>644</v>
+      </c>
+      <c r="W1" t="s">
+        <v>645</v>
+      </c>
+      <c r="X1" t="s">
+        <v>646</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>647</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>648</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.731</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.138</v>
+      </c>
+      <c r="R2" t="n">
+        <v>94</v>
+      </c>
+      <c r="S2" t="n">
+        <v>63</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.91033333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.37933333333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>31.3333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>21</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.3333333333333</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.28966666666667</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>52.3333333333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.764</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.547</v>
+      </c>
+      <c r="R3" t="n">
+        <v>114</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.25466666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.18233333333333</v>
+      </c>
+      <c r="V3" t="n">
+        <v>38</v>
+      </c>
+      <c r="W3" t="n">
+        <v>16.6666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0723333333333336</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>21.3333333333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.437</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>54.6666666666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="R4" t="n">
+        <v>87</v>
+      </c>
+      <c r="S4" t="n">
+        <v>54</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.48666666666667</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.667333333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.819333333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.154</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.339</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.527</v>
+      </c>
+      <c r="R5" t="n">
+        <v>85</v>
+      </c>
+      <c r="S5" t="n">
+        <v>55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.77966666666667</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.17566666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18.3333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.95533333333333</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6.361</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="R6" t="n">
+        <v>117</v>
+      </c>
+      <c r="S6" t="n">
+        <v>49</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.12033333333333</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.996333333333333</v>
+      </c>
+      <c r="V6" t="n">
+        <v>39</v>
+      </c>
+      <c r="W6" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.11666666666667</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>55.3333333333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>65</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.70766666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>21.3333333333333</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.653666666666667</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.333333333333336</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.76166666666667</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.971</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>62</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="V8" t="n">
+        <v>31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.0285</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.9425</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>86</v>
+      </c>
+      <c r="S9" t="n">
+        <v>41</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="V9" t="n">
+        <v>28.6666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>13.6666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>49</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6825</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5665</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.7985</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.425</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.611</v>
+      </c>
+      <c r="R11" t="n">
+        <v>73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>103</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.87033333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.3333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.395333333333333</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.34533333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>58.6666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="R12" t="n">
+        <v>52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11566666666667</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.00433333333333</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17.3333333333333</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20.6666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.111333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.33333333333334</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>68</v>
+      </c>
+      <c r="S13" t="n">
+        <v>79</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.03933333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="V13" t="n">
+        <v>22.6666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.305666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-3.66666666666666</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.38433333333333</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.589</v>
+      </c>
+      <c r="R14" t="n">
+        <v>79</v>
+      </c>
+      <c r="S14" t="n">
+        <v>71</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.54133333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.19633333333333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.3333333333333</v>
+      </c>
+      <c r="W14" t="n">
+        <v>23.6666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.66666666666666</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.73766666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.512</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R15" t="n">
+        <v>93</v>
+      </c>
+      <c r="S15" t="n">
+        <v>122</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.40666666666667</v>
+      </c>
+      <c r="V15" t="n">
+        <v>31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>40.6666666666667</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.0973333333333328</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-9.66666666666666</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.91066666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>71.6666666666667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.231</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="R16" t="n">
+        <v>65</v>
+      </c>
+      <c r="S16" t="n">
+        <v>94</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.41033333333333</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V16" t="n">
+        <v>21.6666666666667</v>
+      </c>
+      <c r="W16" t="n">
+        <v>31.3333333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.399666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-9.66666666666666</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.22033333333333</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.161</v>
+      </c>
+      <c r="R17" t="n">
+        <v>33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>104</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.870666666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.05366666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>34.6666666666667</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.183</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-23.6666666666667</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.92433333333333</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>45.6666666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="R18" t="n">
+        <v>49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>103</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.744333333333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.85033333333333</v>
+      </c>
+      <c r="V18" t="n">
+        <v>16.3333333333333</v>
+      </c>
+      <c r="W18" t="n">
+        <v>34.3333333333333</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.59466666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>50.6666666666667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>8</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>18</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.069</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.077</v>
+      </c>
+      <c r="R19" t="n">
+        <v>66</v>
+      </c>
+      <c r="S19" t="n">
+        <v>85</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.35633333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.69233333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22</v>
+      </c>
+      <c r="W19" t="n">
+        <v>28.3333333333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.336</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-6.33333333333333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.04866666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50.3333333333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>19</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R20" t="n">
+        <v>47</v>
+      </c>
+      <c r="S20" t="n">
+        <v>80</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.15833333333333</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44333333333333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>15.6666666666667</v>
+      </c>
+      <c r="W20" t="n">
+        <v>26.6666666666667</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.285</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.60166666666667</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>42.3333333333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.283</v>
+      </c>
+      <c r="R21" t="n">
+        <v>58</v>
+      </c>
+      <c r="S21" t="n">
+        <v>70</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.06833333333333</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.42766666666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>19.3333333333333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>23.3333333333333</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.359333333333333</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.496</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>42.6666666666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>21</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="V22" t="n">
+        <v>13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.219</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>22</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="R23" t="n">
+        <v>14</v>
+      </c>
+      <c r="S23" t="n">
+        <v>24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V23" t="n">
+        <v>14</v>
+      </c>
+      <c r="W23" t="n">
+        <v>24</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.903</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E1" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J1" t="s">
+        <v>659</v>
+      </c>
+      <c r="K1" t="s">
+        <v>660</v>
+      </c>
+      <c r="L1" t="s">
+        <v>661</v>
+      </c>
+      <c r="M1" t="s">
+        <v>662</v>
+      </c>
+      <c r="N1" t="s">
+        <v>663</v>
+      </c>
+      <c r="O1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P1" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>700</v>
+      </c>
+      <c r="I2" t="s">
+        <v>730</v>
+      </c>
+      <c r="J2" t="s">
+        <v>760</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>701</v>
+      </c>
+      <c r="I3" t="s">
+        <v>731</v>
+      </c>
+      <c r="J3" t="s">
+        <v>761</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>692</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>702</v>
+      </c>
+      <c r="I4" t="s">
+        <v>732</v>
+      </c>
+      <c r="J4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B5" t="s">
+        <v>681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>703</v>
+      </c>
+      <c r="I5" t="s">
+        <v>733</v>
+      </c>
+      <c r="J5" t="s">
+        <v>763</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" t="s">
+        <v>682</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>704</v>
+      </c>
+      <c r="I6" t="s">
+        <v>734</v>
+      </c>
+      <c r="J6" t="s">
+        <v>764</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>688</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>705</v>
+      </c>
+      <c r="I7" t="s">
+        <v>735</v>
+      </c>
+      <c r="J7" t="s">
+        <v>765</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>706</v>
+      </c>
+      <c r="I8" t="s">
+        <v>736</v>
+      </c>
+      <c r="J8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B9" t="s">
+        <v>685</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>697</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>707</v>
+      </c>
+      <c r="I9" t="s">
+        <v>737</v>
+      </c>
+      <c r="J9" t="s">
+        <v>767</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" t="s">
+        <v>686</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>689</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>708</v>
+      </c>
+      <c r="I10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J10" t="s">
+        <v>768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>670</v>
+      </c>
+      <c r="B11" t="s">
+        <v>687</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>709</v>
+      </c>
+      <c r="I11" t="s">
+        <v>739</v>
+      </c>
+      <c r="J11" t="s">
+        <v>769</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>687</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>710</v>
+      </c>
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+      <c r="J12" t="s">
+        <v>770</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>671</v>
+      </c>
+      <c r="B13" t="s">
+        <v>689</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>685</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>711</v>
+      </c>
+      <c r="I13" t="s">
+        <v>741</v>
+      </c>
+      <c r="J13" t="s">
+        <v>771</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B14" t="s">
+        <v>690</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>683</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>712</v>
+      </c>
+      <c r="I14" t="s">
+        <v>742</v>
+      </c>
+      <c r="J14" t="s">
+        <v>772</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>682</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>713</v>
+      </c>
+      <c r="I15" t="s">
+        <v>743</v>
+      </c>
+      <c r="J15" t="s">
+        <v>773</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B16" t="s">
+        <v>692</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>678</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>714</v>
+      </c>
+      <c r="I16" t="s">
+        <v>744</v>
+      </c>
+      <c r="J16" t="s">
+        <v>774</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>671</v>
+      </c>
+      <c r="B17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>715</v>
+      </c>
+      <c r="I17" t="s">
+        <v>745</v>
+      </c>
+      <c r="J17" t="s">
+        <v>775</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B18" t="s">
+        <v>694</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>716</v>
+      </c>
+      <c r="I18" t="s">
+        <v>746</v>
+      </c>
+      <c r="J18" t="s">
+        <v>776</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B19" t="s">
+        <v>695</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>679</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>717</v>
+      </c>
+      <c r="I19" t="s">
+        <v>747</v>
+      </c>
+      <c r="J19" t="s">
+        <v>777</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>673</v>
+      </c>
+      <c r="B20" t="s">
+        <v>696</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>686</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>718</v>
+      </c>
+      <c r="I20" t="s">
+        <v>748</v>
+      </c>
+      <c r="J20" t="s">
+        <v>778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>673</v>
+      </c>
+      <c r="B21" t="s">
+        <v>697</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>719</v>
+      </c>
+      <c r="I21" t="s">
+        <v>749</v>
+      </c>
+      <c r="J21" t="s">
+        <v>779</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>674</v>
+      </c>
+      <c r="B22" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>689</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>720</v>
+      </c>
+      <c r="I22" t="s">
+        <v>750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>780</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>674</v>
+      </c>
+      <c r="B23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>699</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>721</v>
+      </c>
+      <c r="I23" t="s">
+        <v>751</v>
+      </c>
+      <c r="J23" t="s">
+        <v>781</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>674</v>
+      </c>
+      <c r="B24" t="s">
+        <v>679</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>686</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>722</v>
+      </c>
+      <c r="I24" t="s">
+        <v>752</v>
+      </c>
+      <c r="J24" t="s">
+        <v>782</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>674</v>
+      </c>
+      <c r="B25" t="s">
+        <v>684</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>692</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>723</v>
+      </c>
+      <c r="I25" t="s">
+        <v>753</v>
+      </c>
+      <c r="J25" t="s">
+        <v>783</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" t="s">
+        <v>698</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>694</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>724</v>
+      </c>
+      <c r="I26" t="s">
+        <v>754</v>
+      </c>
+      <c r="J26" t="s">
+        <v>784</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>674</v>
+      </c>
+      <c r="B27" t="s">
+        <v>680</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>725</v>
+      </c>
+      <c r="I27" t="s">
+        <v>755</v>
+      </c>
+      <c r="J27" t="s">
+        <v>785</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>675</v>
+      </c>
+      <c r="B28" t="s">
+        <v>691</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>726</v>
+      </c>
+      <c r="I28" t="s">
+        <v>756</v>
+      </c>
+      <c r="J28" t="s">
+        <v>786</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" t="s">
+        <v>682</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>696</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>727</v>
+      </c>
+      <c r="I29" t="s">
+        <v>757</v>
+      </c>
+      <c r="J29" t="s">
+        <v>787</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>677</v>
+      </c>
+      <c r="B30" t="s">
+        <v>697</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>690</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H30" t="s">
+        <v>728</v>
+      </c>
+      <c r="I30" t="s">
+        <v>758</v>
+      </c>
+      <c r="J30" t="s">
+        <v>788</v>
+      </c>
+      <c r="K30" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>677</v>
+      </c>
+      <c r="B31" t="s">
+        <v>687</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>681</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H31" t="s">
+        <v>729</v>
+      </c>
+      <c r="I31" t="s">
+        <v>759</v>
+      </c>
+      <c r="J31" t="s">
+        <v>789</v>
+      </c>
+      <c r="K31" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>677</v>
+      </c>
+      <c r="B32" t="s">
+        <v>687</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>681</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H32" t="s">
+        <v>729</v>
+      </c>
+      <c r="I32" t="s">
+        <v>759</v>
+      </c>
+      <c r="J32" t="s">
+        <v>789</v>
+      </c>
+      <c r="K32" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="7"/>
+    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -95377,7 +95377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>

--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="8" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="9"/>
+    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -3719,6 +3719,1610 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C1" t="s">
+        <v>652</v>
+      </c>
+      <c r="D1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E1" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J1" t="s">
+        <v>659</v>
+      </c>
+      <c r="K1" t="s">
+        <v>660</v>
+      </c>
+      <c r="L1" t="s">
+        <v>661</v>
+      </c>
+      <c r="M1" t="s">
+        <v>662</v>
+      </c>
+      <c r="N1" t="s">
+        <v>663</v>
+      </c>
+      <c r="O1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P1" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H2" t="s">
+        <v>700</v>
+      </c>
+      <c r="I2" t="s">
+        <v>730</v>
+      </c>
+      <c r="J2" t="s">
+        <v>760</v>
+      </c>
+      <c r="K2" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>701</v>
+      </c>
+      <c r="I3" t="s">
+        <v>731</v>
+      </c>
+      <c r="J3" t="s">
+        <v>761</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>692</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>702</v>
+      </c>
+      <c r="I4" t="s">
+        <v>732</v>
+      </c>
+      <c r="J4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.617</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B5" t="s">
+        <v>681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H5" t="s">
+        <v>703</v>
+      </c>
+      <c r="I5" t="s">
+        <v>733</v>
+      </c>
+      <c r="J5" t="s">
+        <v>763</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.251</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" t="s">
+        <v>682</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>690</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>704</v>
+      </c>
+      <c r="I6" t="s">
+        <v>734</v>
+      </c>
+      <c r="J6" t="s">
+        <v>764</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B7" t="s">
+        <v>683</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>688</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>705</v>
+      </c>
+      <c r="I7" t="s">
+        <v>735</v>
+      </c>
+      <c r="J7" t="s">
+        <v>765</v>
+      </c>
+      <c r="K7" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>706</v>
+      </c>
+      <c r="I8" t="s">
+        <v>736</v>
+      </c>
+      <c r="J8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.642</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B9" t="s">
+        <v>685</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>697</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>707</v>
+      </c>
+      <c r="I9" t="s">
+        <v>737</v>
+      </c>
+      <c r="J9" t="s">
+        <v>767</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" t="s">
+        <v>686</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>689</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>708</v>
+      </c>
+      <c r="I10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J10" t="s">
+        <v>768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>670</v>
+      </c>
+      <c r="B11" t="s">
+        <v>687</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>709</v>
+      </c>
+      <c r="I11" t="s">
+        <v>739</v>
+      </c>
+      <c r="J11" t="s">
+        <v>769</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>687</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>710</v>
+      </c>
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+      <c r="J12" t="s">
+        <v>770</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>671</v>
+      </c>
+      <c r="B13" t="s">
+        <v>689</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>685</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>711</v>
+      </c>
+      <c r="I13" t="s">
+        <v>741</v>
+      </c>
+      <c r="J13" t="s">
+        <v>771</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B14" t="s">
+        <v>690</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>683</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H14" t="s">
+        <v>712</v>
+      </c>
+      <c r="I14" t="s">
+        <v>742</v>
+      </c>
+      <c r="J14" t="s">
+        <v>772</v>
+      </c>
+      <c r="K14" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.576</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" t="s">
+        <v>691</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>682</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="s">
+        <v>713</v>
+      </c>
+      <c r="I15" t="s">
+        <v>743</v>
+      </c>
+      <c r="J15" t="s">
+        <v>773</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B16" t="s">
+        <v>692</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>678</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H16" t="s">
+        <v>714</v>
+      </c>
+      <c r="I16" t="s">
+        <v>744</v>
+      </c>
+      <c r="J16" t="s">
+        <v>774</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>671</v>
+      </c>
+      <c r="B17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>684</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>715</v>
+      </c>
+      <c r="I17" t="s">
+        <v>745</v>
+      </c>
+      <c r="J17" t="s">
+        <v>775</v>
+      </c>
+      <c r="K17" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.152</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B18" t="s">
+        <v>694</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>681</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H18" t="s">
+        <v>716</v>
+      </c>
+      <c r="I18" t="s">
+        <v>746</v>
+      </c>
+      <c r="J18" t="s">
+        <v>776</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>673</v>
+      </c>
+      <c r="B19" t="s">
+        <v>695</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>679</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>717</v>
+      </c>
+      <c r="I19" t="s">
+        <v>747</v>
+      </c>
+      <c r="J19" t="s">
+        <v>777</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>673</v>
+      </c>
+      <c r="B20" t="s">
+        <v>696</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>686</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H20" t="s">
+        <v>718</v>
+      </c>
+      <c r="I20" t="s">
+        <v>748</v>
+      </c>
+      <c r="J20" t="s">
+        <v>778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>673</v>
+      </c>
+      <c r="B21" t="s">
+        <v>697</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>680</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>719</v>
+      </c>
+      <c r="I21" t="s">
+        <v>749</v>
+      </c>
+      <c r="J21" t="s">
+        <v>779</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>674</v>
+      </c>
+      <c r="B22" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>689</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H22" t="s">
+        <v>720</v>
+      </c>
+      <c r="I22" t="s">
+        <v>750</v>
+      </c>
+      <c r="J22" t="s">
+        <v>780</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>674</v>
+      </c>
+      <c r="B23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>699</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H23" t="s">
+        <v>721</v>
+      </c>
+      <c r="I23" t="s">
+        <v>751</v>
+      </c>
+      <c r="J23" t="s">
+        <v>781</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>674</v>
+      </c>
+      <c r="B24" t="s">
+        <v>679</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>686</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>722</v>
+      </c>
+      <c r="I24" t="s">
+        <v>752</v>
+      </c>
+      <c r="J24" t="s">
+        <v>782</v>
+      </c>
+      <c r="K24" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="P24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>674</v>
+      </c>
+      <c r="B25" t="s">
+        <v>684</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>692</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H25" t="s">
+        <v>723</v>
+      </c>
+      <c r="I25" t="s">
+        <v>753</v>
+      </c>
+      <c r="J25" t="s">
+        <v>783</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" t="s">
+        <v>698</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>694</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H26" t="s">
+        <v>724</v>
+      </c>
+      <c r="I26" t="s">
+        <v>754</v>
+      </c>
+      <c r="J26" t="s">
+        <v>784</v>
+      </c>
+      <c r="K26" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>674</v>
+      </c>
+      <c r="B27" t="s">
+        <v>680</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>688</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="s">
+        <v>725</v>
+      </c>
+      <c r="I27" t="s">
+        <v>755</v>
+      </c>
+      <c r="J27" t="s">
+        <v>785</v>
+      </c>
+      <c r="K27" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>675</v>
+      </c>
+      <c r="B28" t="s">
+        <v>691</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="s">
+        <v>695</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="s">
+        <v>726</v>
+      </c>
+      <c r="I28" t="s">
+        <v>756</v>
+      </c>
+      <c r="J28" t="s">
+        <v>786</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" t="s">
+        <v>682</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>696</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>727</v>
+      </c>
+      <c r="I29" t="s">
+        <v>757</v>
+      </c>
+      <c r="J29" t="s">
+        <v>787</v>
+      </c>
+      <c r="K29" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>677</v>
+      </c>
+      <c r="B30" t="s">
+        <v>697</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>690</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H30" t="s">
+        <v>728</v>
+      </c>
+      <c r="I30" t="s">
+        <v>758</v>
+      </c>
+      <c r="J30" t="s">
+        <v>788</v>
+      </c>
+      <c r="K30" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>677</v>
+      </c>
+      <c r="B31" t="s">
+        <v>687</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>681</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H31" t="s">
+        <v>729</v>
+      </c>
+      <c r="I31" t="s">
+        <v>759</v>
+      </c>
+      <c r="J31" t="s">
+        <v>789</v>
+      </c>
+      <c r="K31" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>677</v>
+      </c>
+      <c r="B32" t="s">
+        <v>687</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>681</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H32" t="s">
+        <v>729</v>
+      </c>
+      <c r="I32" t="s">
+        <v>759</v>
+      </c>
+      <c r="J32" t="s">
+        <v>789</v>
+      </c>
+      <c r="K32" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.358</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
@@ -95375,1608 +96979,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>650</v>
-      </c>
-      <c r="B1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C1" t="s">
-        <v>652</v>
-      </c>
-      <c r="D1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E1" t="s">
-        <v>654</v>
-      </c>
-      <c r="F1" t="s">
-        <v>655</v>
-      </c>
-      <c r="G1" t="s">
-        <v>656</v>
-      </c>
-      <c r="H1" t="s">
-        <v>657</v>
-      </c>
-      <c r="I1" t="s">
-        <v>658</v>
-      </c>
-      <c r="J1" t="s">
-        <v>659</v>
-      </c>
-      <c r="K1" t="s">
-        <v>660</v>
-      </c>
-      <c r="L1" t="s">
-        <v>661</v>
-      </c>
-      <c r="M1" t="s">
-        <v>662</v>
-      </c>
-      <c r="N1" t="s">
-        <v>663</v>
-      </c>
-      <c r="O1" t="s">
-        <v>664</v>
-      </c>
-      <c r="P1" t="s">
-        <v>665</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B2" t="s">
-        <v>678</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>695</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H2" t="s">
-        <v>700</v>
-      </c>
-      <c r="I2" t="s">
-        <v>730</v>
-      </c>
-      <c r="J2" t="s">
-        <v>760</v>
-      </c>
-      <c r="K2" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>667</v>
-      </c>
-      <c r="B3" t="s">
-        <v>679</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>693</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>701</v>
-      </c>
-      <c r="I3" t="s">
-        <v>731</v>
-      </c>
-      <c r="J3" t="s">
-        <v>761</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>667</v>
-      </c>
-      <c r="B4" t="s">
-        <v>680</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>692</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>702</v>
-      </c>
-      <c r="I4" t="s">
-        <v>732</v>
-      </c>
-      <c r="J4" t="s">
-        <v>762</v>
-      </c>
-      <c r="K4" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>667</v>
-      </c>
-      <c r="B5" t="s">
-        <v>681</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>691</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H5" t="s">
-        <v>703</v>
-      </c>
-      <c r="I5" t="s">
-        <v>733</v>
-      </c>
-      <c r="J5" t="s">
-        <v>763</v>
-      </c>
-      <c r="K5" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.251</v>
-      </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>667</v>
-      </c>
-      <c r="B6" t="s">
-        <v>682</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>690</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>704</v>
-      </c>
-      <c r="I6" t="s">
-        <v>734</v>
-      </c>
-      <c r="J6" t="s">
-        <v>764</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B7" t="s">
-        <v>683</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>688</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H7" t="s">
-        <v>705</v>
-      </c>
-      <c r="I7" t="s">
-        <v>735</v>
-      </c>
-      <c r="J7" t="s">
-        <v>765</v>
-      </c>
-      <c r="K7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>56.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.497</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>669</v>
-      </c>
-      <c r="B8" t="s">
-        <v>684</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E8" t="s">
-        <v>696</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>706</v>
-      </c>
-      <c r="I8" t="s">
-        <v>736</v>
-      </c>
-      <c r="J8" t="s">
-        <v>766</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.642</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>669</v>
-      </c>
-      <c r="B9" t="s">
-        <v>685</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>697</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>707</v>
-      </c>
-      <c r="I9" t="s">
-        <v>737</v>
-      </c>
-      <c r="J9" t="s">
-        <v>767</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>670</v>
-      </c>
-      <c r="B10" t="s">
-        <v>686</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E10" t="s">
-        <v>689</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H10" t="s">
-        <v>708</v>
-      </c>
-      <c r="I10" t="s">
-        <v>738</v>
-      </c>
-      <c r="J10" t="s">
-        <v>768</v>
-      </c>
-      <c r="K10" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.719</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>670</v>
-      </c>
-      <c r="B11" t="s">
-        <v>687</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E11" t="s">
-        <v>694</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" t="s">
-        <v>709</v>
-      </c>
-      <c r="I11" t="s">
-        <v>739</v>
-      </c>
-      <c r="J11" t="s">
-        <v>769</v>
-      </c>
-      <c r="K11" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.419</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>671</v>
-      </c>
-      <c r="B12" t="s">
-        <v>688</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E12" t="s">
-        <v>687</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H12" t="s">
-        <v>710</v>
-      </c>
-      <c r="I12" t="s">
-        <v>740</v>
-      </c>
-      <c r="J12" t="s">
-        <v>770</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>671</v>
-      </c>
-      <c r="B13" t="s">
-        <v>689</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>685</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H13" t="s">
-        <v>711</v>
-      </c>
-      <c r="I13" t="s">
-        <v>741</v>
-      </c>
-      <c r="J13" t="s">
-        <v>771</v>
-      </c>
-      <c r="K13" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.826</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>671</v>
-      </c>
-      <c r="B14" t="s">
-        <v>690</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>683</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="H14" t="s">
-        <v>712</v>
-      </c>
-      <c r="I14" t="s">
-        <v>742</v>
-      </c>
-      <c r="J14" t="s">
-        <v>772</v>
-      </c>
-      <c r="K14" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.576</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>671</v>
-      </c>
-      <c r="B15" t="s">
-        <v>691</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E15" t="s">
-        <v>682</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H15" t="s">
-        <v>713</v>
-      </c>
-      <c r="I15" t="s">
-        <v>743</v>
-      </c>
-      <c r="J15" t="s">
-        <v>773</v>
-      </c>
-      <c r="K15" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.895</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>671</v>
-      </c>
-      <c r="B16" t="s">
-        <v>692</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E16" t="s">
-        <v>678</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H16" t="s">
-        <v>714</v>
-      </c>
-      <c r="I16" t="s">
-        <v>744</v>
-      </c>
-      <c r="J16" t="s">
-        <v>774</v>
-      </c>
-      <c r="K16" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>671</v>
-      </c>
-      <c r="B17" t="s">
-        <v>693</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>684</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H17" t="s">
-        <v>715</v>
-      </c>
-      <c r="I17" t="s">
-        <v>745</v>
-      </c>
-      <c r="J17" t="s">
-        <v>775</v>
-      </c>
-      <c r="K17" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.152</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>672</v>
-      </c>
-      <c r="B18" t="s">
-        <v>694</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>681</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H18" t="s">
-        <v>716</v>
-      </c>
-      <c r="I18" t="s">
-        <v>746</v>
-      </c>
-      <c r="J18" t="s">
-        <v>776</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>673</v>
-      </c>
-      <c r="B19" t="s">
-        <v>695</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>679</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="H19" t="s">
-        <v>717</v>
-      </c>
-      <c r="I19" t="s">
-        <v>747</v>
-      </c>
-      <c r="J19" t="s">
-        <v>777</v>
-      </c>
-      <c r="K19" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.825</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>673</v>
-      </c>
-      <c r="B20" t="s">
-        <v>696</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>686</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>718</v>
-      </c>
-      <c r="I20" t="s">
-        <v>748</v>
-      </c>
-      <c r="J20" t="s">
-        <v>778</v>
-      </c>
-      <c r="K20" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>673</v>
-      </c>
-      <c r="B21" t="s">
-        <v>697</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>680</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="H21" t="s">
-        <v>719</v>
-      </c>
-      <c r="I21" t="s">
-        <v>749</v>
-      </c>
-      <c r="J21" t="s">
-        <v>779</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>674</v>
-      </c>
-      <c r="B22" t="s">
-        <v>683</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>689</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H22" t="s">
-        <v>720</v>
-      </c>
-      <c r="I22" t="s">
-        <v>750</v>
-      </c>
-      <c r="J22" t="s">
-        <v>780</v>
-      </c>
-      <c r="K22" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>674</v>
-      </c>
-      <c r="B23" t="s">
-        <v>678</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>699</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="H23" t="s">
-        <v>721</v>
-      </c>
-      <c r="I23" t="s">
-        <v>751</v>
-      </c>
-      <c r="J23" t="s">
-        <v>781</v>
-      </c>
-      <c r="K23" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.194</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>674</v>
-      </c>
-      <c r="B24" t="s">
-        <v>679</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E24" t="s">
-        <v>686</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H24" t="s">
-        <v>722</v>
-      </c>
-      <c r="I24" t="s">
-        <v>752</v>
-      </c>
-      <c r="J24" t="s">
-        <v>782</v>
-      </c>
-      <c r="K24" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.575</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.806</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>674</v>
-      </c>
-      <c r="B25" t="s">
-        <v>684</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E25" t="s">
-        <v>692</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H25" t="s">
-        <v>723</v>
-      </c>
-      <c r="I25" t="s">
-        <v>753</v>
-      </c>
-      <c r="J25" t="s">
-        <v>783</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.367</v>
-      </c>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>674</v>
-      </c>
-      <c r="B26" t="s">
-        <v>698</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>694</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="H26" t="s">
-        <v>724</v>
-      </c>
-      <c r="I26" t="s">
-        <v>754</v>
-      </c>
-      <c r="J26" t="s">
-        <v>784</v>
-      </c>
-      <c r="K26" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>674</v>
-      </c>
-      <c r="B27" t="s">
-        <v>680</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="E27" t="s">
-        <v>688</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H27" t="s">
-        <v>725</v>
-      </c>
-      <c r="I27" t="s">
-        <v>755</v>
-      </c>
-      <c r="J27" t="s">
-        <v>785</v>
-      </c>
-      <c r="K27" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>675</v>
-      </c>
-      <c r="B28" t="s">
-        <v>691</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E28" t="s">
-        <v>695</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" t="s">
-        <v>726</v>
-      </c>
-      <c r="I28" t="s">
-        <v>756</v>
-      </c>
-      <c r="J28" t="s">
-        <v>786</v>
-      </c>
-      <c r="K28" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>676</v>
-      </c>
-      <c r="B29" t="s">
-        <v>682</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>696</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H29" t="s">
-        <v>727</v>
-      </c>
-      <c r="I29" t="s">
-        <v>757</v>
-      </c>
-      <c r="J29" t="s">
-        <v>787</v>
-      </c>
-      <c r="K29" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>677</v>
-      </c>
-      <c r="B30" t="s">
-        <v>697</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="E30" t="s">
-        <v>690</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H30" t="s">
-        <v>728</v>
-      </c>
-      <c r="I30" t="s">
-        <v>758</v>
-      </c>
-      <c r="J30" t="s">
-        <v>788</v>
-      </c>
-      <c r="K30" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.065</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.334</v>
-      </c>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>677</v>
-      </c>
-      <c r="B31" t="s">
-        <v>687</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E31" t="s">
-        <v>681</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H31" t="s">
-        <v>729</v>
-      </c>
-      <c r="I31" t="s">
-        <v>759</v>
-      </c>
-      <c r="J31" t="s">
-        <v>789</v>
-      </c>
-      <c r="K31" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.967</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P31" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>677</v>
-      </c>
-      <c r="B32" t="s">
-        <v>687</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E32" t="s">
-        <v>681</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H32" t="s">
-        <v>729</v>
-      </c>
-      <c r="I32" t="s">
-        <v>759</v>
-      </c>
-      <c r="J32" t="s">
-        <v>789</v>
-      </c>
-      <c r="K32" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.967</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P32" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>
--- a/data/KKD2526.xlsx
+++ b/data/KKD2526.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Stand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Player xG" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Shots" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stand2" sheetId="10" state="visible" r:id="rId6"/>
-    <sheet name="Wedstrijden2" r:id="rId10" sheetId="11"/>
+    <sheet name="Stand2" sheetId="12" state="visible" r:id="rId6"/>
+    <sheet name="Wedstrijden2" r:id="rId10" sheetId="13"/>
   </sheets>
 </workbook>
 </file>
@@ -3719,7 +3719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
